--- a/scenarios/Coal_Flexibilisation/sub_scenarios/extendable_technologies.xlsx
+++ b/scenarios/Coal_Flexibilisation/sub_scenarios/extendable_technologies.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5996" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5768" uniqueCount="111">
   <si>
     <t>component</t>
   </si>
@@ -350,15 +350,6 @@
   </si>
   <si>
     <t>DLY_3GW_GAS</t>
-  </si>
-  <si>
-    <t>LST_HIGH</t>
-  </si>
-  <si>
-    <t>LST_LOW</t>
-  </si>
-  <si>
-    <t>LST_TOT</t>
   </si>
 </sst>
 </file>
@@ -700,7 +691,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -918,24 +909,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -70004,7 +69977,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AU40"/>
+  <dimension ref="A1:AP2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30.428571428571427" customWidth="1"/>
@@ -70013,10 +69986,10 @@
     <col min="4" max="4" width="14.428571428571429" customWidth="1"/>
     <col min="5" max="5" width="19.428571428571427" customWidth="1"/>
     <col min="6" max="6" width="16.428571428571427" customWidth="1"/>
-    <col min="7" max="47" width="9.285714285714286" customWidth="1"/>
+    <col min="7" max="42" width="9.285714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="1" ht="20.25" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A1" s="57" t="s">
         <v>34</v>
       </c>
@@ -70035,98 +70008,98 @@
       <c r="F1" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="38">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="38">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="38">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="38">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="38">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="38">
+      <c r="G1">
         <v>2025</v>
       </c>
-      <c r="M1" s="38">
+      <c r="H1">
         <v>2026</v>
       </c>
-      <c r="N1" s="38">
+      <c r="I1">
         <v>2027</v>
       </c>
-      <c r="O1" s="38">
+      <c r="J1">
         <v>2028</v>
       </c>
-      <c r="P1" s="38">
+      <c r="K1">
         <v>2029</v>
       </c>
-      <c r="Q1" s="38">
+      <c r="L1">
         <v>2030</v>
       </c>
-      <c r="R1" s="38">
+      <c r="M1">
         <v>2031</v>
       </c>
-      <c r="S1" s="38">
-        <f>R1+1</f>
-      </c>
-      <c r="T1" s="38">
-        <f>S1+1</f>
-      </c>
-      <c r="U1" s="38">
-        <f>T1+1</f>
-      </c>
-      <c r="V1" s="38">
+      <c r="N1">
+        <v>2032</v>
+      </c>
+      <c r="O1">
+        <v>2033</v>
+      </c>
+      <c r="P1">
+        <v>2034</v>
+      </c>
+      <c r="Q1">
         <v>2035</v>
       </c>
-      <c r="W1" s="38">
-        <f>V1+1</f>
-      </c>
-      <c r="X1" s="38">
-        <f>W1+1</f>
-      </c>
-      <c r="Y1" s="38">
-        <f>X1+1</f>
-      </c>
-      <c r="Z1" s="38">
-        <f>Y1+1</f>
-      </c>
-      <c r="AA1" s="38">
+      <c r="R1">
+        <v>2036</v>
+      </c>
+      <c r="S1">
+        <v>2037</v>
+      </c>
+      <c r="T1">
+        <v>2038</v>
+      </c>
+      <c r="U1">
+        <v>2039</v>
+      </c>
+      <c r="V1">
         <v>2040</v>
       </c>
-      <c r="AB1" s="38">
-        <f>AA1+1</f>
-      </c>
-      <c r="AC1" s="38">
-        <f>AB1+1</f>
-      </c>
-      <c r="AD1" s="38">
-        <f>AC1+1</f>
-      </c>
-      <c r="AE1" s="38">
-        <f>AD1+1</f>
-      </c>
-      <c r="AF1" s="38">
+      <c r="W1">
+        <v>2041</v>
+      </c>
+      <c r="X1">
+        <v>2042</v>
+      </c>
+      <c r="Y1">
+        <v>2043</v>
+      </c>
+      <c r="Z1">
+        <v>2044</v>
+      </c>
+      <c r="AA1">
         <v>2045</v>
       </c>
-      <c r="AG1" s="38">
+      <c r="AB1">
+        <v>2046</v>
+      </c>
+      <c r="AC1">
+        <v>2047</v>
+      </c>
+      <c r="AD1">
+        <v>2048</v>
+      </c>
+      <c r="AE1">
+        <v>2049</v>
+      </c>
+      <c r="AF1">
+        <v>2050</v>
+      </c>
+      <c r="AG1" s="39">
         <f>AF1+1</f>
       </c>
-      <c r="AH1" s="38">
+      <c r="AH1" s="39">
         <f>AG1+1</f>
       </c>
-      <c r="AI1" s="38">
+      <c r="AI1" s="39">
         <f>AH1+1</f>
       </c>
-      <c r="AJ1" s="38">
+      <c r="AJ1" s="39">
         <f>AI1+1</f>
       </c>
-      <c r="AK1" s="38">
-        <v>2050</v>
+      <c r="AK1" s="39">
+        <f>AJ1+1</f>
       </c>
       <c r="AL1" s="39">
         <f>AK1+1</f>
@@ -70143,23 +70116,8 @@
       <c r="AP1" s="39">
         <f>AO1+1</f>
       </c>
-      <c r="AQ1" s="39">
-        <f>AP1+1</f>
-      </c>
-      <c r="AR1" s="39">
-        <f>AQ1+1</f>
-      </c>
-      <c r="AS1" s="39">
-        <f>AR1+1</f>
-      </c>
-      <c r="AT1" s="39">
-        <f>AS1+1</f>
-      </c>
-      <c r="AU1" s="39">
-        <f>AT1+1</f>
-      </c>
     </row>
-    <row r="2" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A2" s="67" t="s">
         <v>93</v>
       </c>
@@ -70181,10 +70139,18 @@
       <c r="G2" s="71" t="s">
         <v>102</v>
       </c>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
+      <c r="H2" s="71" t="s">
+        <v>102</v>
+      </c>
+      <c r="I2" s="71" t="s">
+        <v>102</v>
+      </c>
+      <c r="J2" s="71" t="s">
+        <v>102</v>
+      </c>
+      <c r="K2" s="71" t="s">
+        <v>102</v>
+      </c>
       <c r="L2" s="71" t="s">
         <v>102</v>
       </c>
@@ -70245,23 +70211,23 @@
       <c r="AE2" s="71" t="s">
         <v>102</v>
       </c>
-      <c r="AF2" s="71" t="s">
-        <v>102</v>
-      </c>
-      <c r="AG2" s="71" t="s">
-        <v>102</v>
-      </c>
-      <c r="AH2" s="71" t="s">
-        <v>102</v>
-      </c>
-      <c r="AI2" s="71" t="s">
-        <v>102</v>
-      </c>
-      <c r="AJ2" s="71" t="s">
-        <v>102</v>
-      </c>
-      <c r="AK2" s="71">
+      <c r="AF2" s="71">
+        <f>AA2</f>
+      </c>
+      <c r="AG2" s="51">
         <f>AF2</f>
+      </c>
+      <c r="AH2" s="51">
+        <f>AG2</f>
+      </c>
+      <c r="AI2" s="51">
+        <f>AH2</f>
+      </c>
+      <c r="AJ2" s="51">
+        <f>AI2</f>
+      </c>
+      <c r="AK2" s="51">
+        <f>AJ2</f>
       </c>
       <c r="AL2" s="51">
         <f>AK2</f>
@@ -70277,5075 +70243,6 @@
       </c>
       <c r="AP2" s="51">
         <f>AO2</f>
-      </c>
-      <c r="AQ2" s="51">
-        <f>AP2</f>
-      </c>
-      <c r="AR2" s="51">
-        <f>AQ2</f>
-      </c>
-      <c r="AS2" s="51">
-        <f>AR2</f>
-      </c>
-      <c r="AT2" s="51">
-        <f>AS2</f>
-      </c>
-      <c r="AU2" s="51">
-        <f>AT2</f>
-      </c>
-    </row>
-    <row r="3" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A3" s="61" t="s">
-        <v>101</v>
-      </c>
-      <c r="B3" s="41">
-        <v>1</v>
-      </c>
-      <c r="C3" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D3" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="78" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="78" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43">
-        <v>0</v>
-      </c>
-      <c r="M3" s="43">
-        <v>0</v>
-      </c>
-      <c r="N3" s="43">
-        <v>0</v>
-      </c>
-      <c r="O3" s="43">
-        <v>0</v>
-      </c>
-      <c r="P3" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="43">
-        <v>10000</v>
-      </c>
-      <c r="R3" s="43">
-        <v>10000</v>
-      </c>
-      <c r="S3" s="43">
-        <v>10000</v>
-      </c>
-      <c r="T3" s="43">
-        <v>10000</v>
-      </c>
-      <c r="U3" s="43">
-        <v>10000</v>
-      </c>
-      <c r="V3" s="43">
-        <v>10000</v>
-      </c>
-      <c r="W3" s="43">
-        <v>10000</v>
-      </c>
-      <c r="X3" s="43">
-        <v>10000</v>
-      </c>
-      <c r="Y3" s="43">
-        <v>10000</v>
-      </c>
-      <c r="Z3" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AA3" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AB3" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AC3" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AD3" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AE3" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AF3" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AG3" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AH3" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AI3" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AJ3" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AK3" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AL3" s="43">
-        <f>AK3</f>
-      </c>
-      <c r="AM3" s="43">
-        <f>AL3</f>
-      </c>
-      <c r="AN3" s="43">
-        <f>AM3</f>
-      </c>
-      <c r="AO3" s="43">
-        <f>AN3</f>
-      </c>
-      <c r="AP3" s="43">
-        <f>AO3</f>
-      </c>
-      <c r="AQ3" s="43">
-        <f>AP3</f>
-      </c>
-      <c r="AR3" s="43">
-        <f>AQ3</f>
-      </c>
-      <c r="AS3" s="43">
-        <f>AR3</f>
-      </c>
-      <c r="AT3" s="43">
-        <f>AS3</f>
-      </c>
-      <c r="AU3" s="43">
-        <f>AT3</f>
-      </c>
-    </row>
-    <row r="4" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A4" s="61">
-        <f>A3</f>
-      </c>
-      <c r="B4" s="41">
-        <v>1</v>
-      </c>
-      <c r="C4" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D4" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="78" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="78" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43">
-        <v>2000</v>
-      </c>
-      <c r="M4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="N4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="O4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="P4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="Q4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="R4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="S4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="T4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="U4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="V4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="W4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="X4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="Y4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="Z4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AA4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AB4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AC4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AD4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AE4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AF4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AG4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AH4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AI4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AJ4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AK4" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AL4" s="43">
-        <f>AK4</f>
-      </c>
-      <c r="AM4" s="43">
-        <f>AL4</f>
-      </c>
-      <c r="AN4" s="43">
-        <f>AM4</f>
-      </c>
-      <c r="AO4" s="43">
-        <f>AN4</f>
-      </c>
-      <c r="AP4" s="43">
-        <f>AO4</f>
-      </c>
-      <c r="AQ4" s="43">
-        <f>AP4</f>
-      </c>
-      <c r="AR4" s="43">
-        <f>AQ4</f>
-      </c>
-      <c r="AS4" s="43">
-        <f>AR4</f>
-      </c>
-      <c r="AT4" s="43">
-        <f>AS4</f>
-      </c>
-      <c r="AU4" s="43">
-        <f>AT4</f>
-      </c>
-    </row>
-    <row r="5" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A5" s="61">
-        <f>A4</f>
-      </c>
-      <c r="B5" s="41">
-        <v>1</v>
-      </c>
-      <c r="C5" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D5" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="78" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="78" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43">
-        <v>0</v>
-      </c>
-      <c r="M5" s="43">
-        <v>0</v>
-      </c>
-      <c r="N5" s="43">
-        <v>0</v>
-      </c>
-      <c r="O5" s="43">
-        <v>0</v>
-      </c>
-      <c r="P5" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="43">
-        <v>1000</v>
-      </c>
-      <c r="R5" s="43">
-        <f>Q5</f>
-      </c>
-      <c r="S5" s="43">
-        <f>R5</f>
-      </c>
-      <c r="T5" s="43">
-        <f>S5</f>
-      </c>
-      <c r="U5" s="43">
-        <f>T5</f>
-      </c>
-      <c r="V5" s="43">
-        <f>U5</f>
-      </c>
-      <c r="W5" s="43">
-        <f>V5</f>
-      </c>
-      <c r="X5" s="43">
-        <f>W5</f>
-      </c>
-      <c r="Y5" s="43">
-        <f>X5</f>
-      </c>
-      <c r="Z5" s="43">
-        <f>Y5</f>
-      </c>
-      <c r="AA5" s="43">
-        <f>Z5</f>
-      </c>
-      <c r="AB5" s="43">
-        <f>AA5</f>
-      </c>
-      <c r="AC5" s="43">
-        <f>AB5</f>
-      </c>
-      <c r="AD5" s="43">
-        <f>AC5</f>
-      </c>
-      <c r="AE5" s="43">
-        <f>AD5</f>
-      </c>
-      <c r="AF5" s="43">
-        <f>AE5</f>
-      </c>
-      <c r="AG5" s="43">
-        <f>AF5</f>
-      </c>
-      <c r="AH5" s="43">
-        <f>AG5</f>
-      </c>
-      <c r="AI5" s="43">
-        <f>AH5</f>
-      </c>
-      <c r="AJ5" s="43">
-        <f>AI5</f>
-      </c>
-      <c r="AK5" s="43">
-        <f>AJ5</f>
-      </c>
-      <c r="AL5" s="43">
-        <f>AK5</f>
-      </c>
-      <c r="AM5" s="43">
-        <f>AL5</f>
-      </c>
-      <c r="AN5" s="43">
-        <f>AM5</f>
-      </c>
-      <c r="AO5" s="43">
-        <f>AN5</f>
-      </c>
-      <c r="AP5" s="43">
-        <f>AO5</f>
-      </c>
-      <c r="AQ5" s="43">
-        <f>AP5</f>
-      </c>
-      <c r="AR5" s="43">
-        <f>AQ5</f>
-      </c>
-      <c r="AS5" s="43">
-        <f>AR5</f>
-      </c>
-      <c r="AT5" s="43">
-        <f>AS5</f>
-      </c>
-      <c r="AU5" s="43">
-        <f>AT5</f>
-      </c>
-    </row>
-    <row r="6" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A6" s="61">
-        <f>A5</f>
-      </c>
-      <c r="B6" s="41">
-        <v>1</v>
-      </c>
-      <c r="C6" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="78" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="78" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="43"/>
-      <c r="L6" s="43">
-        <v>5</v>
-      </c>
-      <c r="M6" s="43">
-        <v>1000</v>
-      </c>
-      <c r="N6" s="43">
-        <f>M6+100</f>
-      </c>
-      <c r="O6" s="43">
-        <f>N6+100</f>
-      </c>
-      <c r="P6" s="43">
-        <f>O6+100</f>
-      </c>
-      <c r="Q6" s="43">
-        <f>P6+100</f>
-      </c>
-      <c r="R6" s="43">
-        <f>Q6+100</f>
-      </c>
-      <c r="S6" s="43">
-        <f>R6+100</f>
-      </c>
-      <c r="T6" s="43">
-        <f>S6+100</f>
-      </c>
-      <c r="U6" s="43">
-        <f>T6+100</f>
-      </c>
-      <c r="V6" s="43">
-        <f>U6+100</f>
-      </c>
-      <c r="W6" s="43">
-        <f>V6+100</f>
-      </c>
-      <c r="X6" s="43">
-        <f>W6+100</f>
-      </c>
-      <c r="Y6" s="43">
-        <f>X6+100</f>
-      </c>
-      <c r="Z6" s="43">
-        <f>Y6+100</f>
-      </c>
-      <c r="AA6" s="43">
-        <f>Z6+100</f>
-      </c>
-      <c r="AB6" s="43">
-        <f>AA6+100</f>
-      </c>
-      <c r="AC6" s="43">
-        <f>AB6+100</f>
-      </c>
-      <c r="AD6" s="43">
-        <f>AC6+100</f>
-      </c>
-      <c r="AE6" s="43">
-        <f>AD6+100</f>
-      </c>
-      <c r="AF6" s="43">
-        <f>AE6+100</f>
-      </c>
-      <c r="AG6" s="43">
-        <f>AF6+100</f>
-      </c>
-      <c r="AH6" s="43">
-        <f>AG6+100</f>
-      </c>
-      <c r="AI6" s="43">
-        <f>AH6+100</f>
-      </c>
-      <c r="AJ6" s="43">
-        <f>AI6+100</f>
-      </c>
-      <c r="AK6" s="43">
-        <f>AJ6+100</f>
-      </c>
-      <c r="AL6" s="43">
-        <f>AK6+100</f>
-      </c>
-      <c r="AM6" s="43">
-        <f>AL6+100</f>
-      </c>
-      <c r="AN6" s="43">
-        <f>AM6+100</f>
-      </c>
-      <c r="AO6" s="43">
-        <f>AN6+100</f>
-      </c>
-      <c r="AP6" s="43">
-        <f>AO6+100</f>
-      </c>
-      <c r="AQ6" s="43">
-        <f>AP6+100</f>
-      </c>
-      <c r="AR6" s="43">
-        <f>AQ6+100</f>
-      </c>
-      <c r="AS6" s="43">
-        <f>AR6+100</f>
-      </c>
-      <c r="AT6" s="43">
-        <f>AS6+100</f>
-      </c>
-      <c r="AU6" s="43">
-        <f>AT6+100</f>
-      </c>
-    </row>
-    <row r="7" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A7" s="61">
-        <f>A6</f>
-      </c>
-      <c r="B7" s="41">
-        <v>1</v>
-      </c>
-      <c r="C7" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D7" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="78" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="78" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="43"/>
-      <c r="L7" s="43">
-        <v>5</v>
-      </c>
-      <c r="M7" s="43">
-        <v>0</v>
-      </c>
-      <c r="N7" s="43">
-        <v>0</v>
-      </c>
-      <c r="O7" s="43">
-        <v>0</v>
-      </c>
-      <c r="P7" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="43">
-        <v>1500</v>
-      </c>
-      <c r="R7" s="43">
-        <f>Q7</f>
-      </c>
-      <c r="S7" s="43">
-        <f>R7</f>
-      </c>
-      <c r="T7" s="43">
-        <f>S7</f>
-      </c>
-      <c r="U7" s="43">
-        <f>T7</f>
-      </c>
-      <c r="V7" s="43">
-        <f>U7</f>
-      </c>
-      <c r="W7" s="43">
-        <f>V7</f>
-      </c>
-      <c r="X7" s="43">
-        <f>W7</f>
-      </c>
-      <c r="Y7" s="43">
-        <f>X7</f>
-      </c>
-      <c r="Z7" s="43">
-        <f>Y7</f>
-      </c>
-      <c r="AA7" s="43">
-        <f>Z7</f>
-      </c>
-      <c r="AB7" s="43">
-        <f>AA7</f>
-      </c>
-      <c r="AC7" s="43">
-        <f>AB7</f>
-      </c>
-      <c r="AD7" s="43">
-        <f>AC7</f>
-      </c>
-      <c r="AE7" s="43">
-        <f>AD7</f>
-      </c>
-      <c r="AF7" s="43">
-        <f>AE7</f>
-      </c>
-      <c r="AG7" s="43">
-        <f>AF7</f>
-      </c>
-      <c r="AH7" s="43">
-        <f>AG7</f>
-      </c>
-      <c r="AI7" s="43">
-        <f>AH7</f>
-      </c>
-      <c r="AJ7" s="43">
-        <f>AI7</f>
-      </c>
-      <c r="AK7" s="43">
-        <f>AJ7</f>
-      </c>
-      <c r="AL7" s="43">
-        <f>AK7</f>
-      </c>
-      <c r="AM7" s="43">
-        <f>AL7</f>
-      </c>
-      <c r="AN7" s="43">
-        <f>AM7</f>
-      </c>
-      <c r="AO7" s="43">
-        <f>AN7</f>
-      </c>
-      <c r="AP7" s="43">
-        <f>AO7</f>
-      </c>
-      <c r="AQ7" s="43">
-        <f>AP7</f>
-      </c>
-      <c r="AR7" s="43">
-        <f>AQ7</f>
-      </c>
-      <c r="AS7" s="43">
-        <f>AR7</f>
-      </c>
-      <c r="AT7" s="43">
-        <f>AS7</f>
-      </c>
-      <c r="AU7" s="43">
-        <f>AT7</f>
-      </c>
-    </row>
-    <row r="8" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A8" s="61">
-        <f>A7</f>
-      </c>
-      <c r="B8" s="41">
-        <v>1</v>
-      </c>
-      <c r="C8" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D8" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="78" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="78" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
-      <c r="L8" s="43">
-        <v>0</v>
-      </c>
-      <c r="M8" s="43">
-        <v>0</v>
-      </c>
-      <c r="N8" s="43">
-        <v>0</v>
-      </c>
-      <c r="O8" s="43">
-        <v>0</v>
-      </c>
-      <c r="P8" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="R8" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="S8" s="43">
-        <f>R8</f>
-      </c>
-      <c r="T8" s="43">
-        <f>S8</f>
-      </c>
-      <c r="U8" s="43">
-        <f>T8</f>
-      </c>
-      <c r="V8" s="43">
-        <f>U8</f>
-      </c>
-      <c r="W8" s="43">
-        <f>V8</f>
-      </c>
-      <c r="X8" s="43">
-        <f>W8</f>
-      </c>
-      <c r="Y8" s="43">
-        <f>X8</f>
-      </c>
-      <c r="Z8" s="43">
-        <f>Y8</f>
-      </c>
-      <c r="AA8" s="43">
-        <f>Z8</f>
-      </c>
-      <c r="AB8" s="43">
-        <f>AA8</f>
-      </c>
-      <c r="AC8" s="43">
-        <f>AB8</f>
-      </c>
-      <c r="AD8" s="43">
-        <f>AC8</f>
-      </c>
-      <c r="AE8" s="43">
-        <f>AD8</f>
-      </c>
-      <c r="AF8" s="43">
-        <f>AE8</f>
-      </c>
-      <c r="AG8" s="43">
-        <f>AF8</f>
-      </c>
-      <c r="AH8" s="43">
-        <f>AG8</f>
-      </c>
-      <c r="AI8" s="43">
-        <f>AH8</f>
-      </c>
-      <c r="AJ8" s="43">
-        <f>AI8</f>
-      </c>
-      <c r="AK8" s="43">
-        <f>AJ8</f>
-      </c>
-      <c r="AL8" s="43">
-        <f>AK8</f>
-      </c>
-      <c r="AM8" s="43">
-        <f>AL8</f>
-      </c>
-      <c r="AN8" s="43">
-        <f>AM8</f>
-      </c>
-      <c r="AO8" s="43">
-        <f>AN8</f>
-      </c>
-      <c r="AP8" s="43">
-        <f>AO8</f>
-      </c>
-      <c r="AQ8" s="43">
-        <f>AP8</f>
-      </c>
-      <c r="AR8" s="43">
-        <f>AQ8</f>
-      </c>
-      <c r="AS8" s="43">
-        <f>AR8</f>
-      </c>
-      <c r="AT8" s="43">
-        <f>AS8</f>
-      </c>
-      <c r="AU8" s="43">
-        <f>AT8</f>
-      </c>
-    </row>
-    <row r="9" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A9" s="61">
-        <f>A8</f>
-      </c>
-      <c r="B9" s="41">
-        <v>1</v>
-      </c>
-      <c r="C9" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D9" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="78" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="78" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="43"/>
-      <c r="K9" s="43"/>
-      <c r="L9" s="43">
-        <v>0</v>
-      </c>
-      <c r="M9" s="43">
-        <v>0</v>
-      </c>
-      <c r="N9" s="43">
-        <v>0</v>
-      </c>
-      <c r="O9" s="43">
-        <v>0</v>
-      </c>
-      <c r="P9" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="R9" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="S9" s="43">
-        <f>R9</f>
-      </c>
-      <c r="T9" s="43">
-        <f>S9</f>
-      </c>
-      <c r="U9" s="43">
-        <f>T9</f>
-      </c>
-      <c r="V9" s="43">
-        <f>U9</f>
-      </c>
-      <c r="W9" s="43">
-        <f>V9</f>
-      </c>
-      <c r="X9" s="43">
-        <f>W9</f>
-      </c>
-      <c r="Y9" s="43">
-        <f>X9</f>
-      </c>
-      <c r="Z9" s="43">
-        <f>Y9</f>
-      </c>
-      <c r="AA9" s="43">
-        <f>Z9</f>
-      </c>
-      <c r="AB9" s="43">
-        <f>AA9</f>
-      </c>
-      <c r="AC9" s="43">
-        <f>AB9</f>
-      </c>
-      <c r="AD9" s="43">
-        <f>AC9</f>
-      </c>
-      <c r="AE9" s="43">
-        <f>AD9</f>
-      </c>
-      <c r="AF9" s="43">
-        <f>AE9</f>
-      </c>
-      <c r="AG9" s="43">
-        <f>AF9</f>
-      </c>
-      <c r="AH9" s="43">
-        <f>AG9</f>
-      </c>
-      <c r="AI9" s="43">
-        <f>AH9</f>
-      </c>
-      <c r="AJ9" s="43">
-        <f>AI9</f>
-      </c>
-      <c r="AK9" s="43">
-        <f>AJ9</f>
-      </c>
-      <c r="AL9" s="43">
-        <f>AK9</f>
-      </c>
-      <c r="AM9" s="43">
-        <f>AL9</f>
-      </c>
-      <c r="AN9" s="43">
-        <f>AM9</f>
-      </c>
-      <c r="AO9" s="43">
-        <f>AN9</f>
-      </c>
-      <c r="AP9" s="43">
-        <f>AO9</f>
-      </c>
-      <c r="AQ9" s="43">
-        <f>AP9</f>
-      </c>
-      <c r="AR9" s="43">
-        <f>AQ9</f>
-      </c>
-      <c r="AS9" s="43">
-        <f>AR9</f>
-      </c>
-      <c r="AT9" s="43">
-        <f>AS9</f>
-      </c>
-      <c r="AU9" s="43">
-        <f>AT9</f>
-      </c>
-    </row>
-    <row r="10" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A10" s="61">
-        <f>A9</f>
-      </c>
-      <c r="B10" s="41">
-        <v>1</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D10" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="78" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="78" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="43"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="43"/>
-      <c r="K10" s="43"/>
-      <c r="L10" s="43">
-        <v>0</v>
-      </c>
-      <c r="M10" s="43">
-        <v>0</v>
-      </c>
-      <c r="N10" s="43">
-        <v>0</v>
-      </c>
-      <c r="O10" s="43">
-        <v>0</v>
-      </c>
-      <c r="P10" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="R10" s="43">
-        <v>0</v>
-      </c>
-      <c r="S10" s="43">
-        <v>0</v>
-      </c>
-      <c r="T10" s="43">
-        <v>0</v>
-      </c>
-      <c r="U10" s="43">
-        <f>T10</f>
-      </c>
-      <c r="V10" s="43">
-        <f>U10</f>
-      </c>
-      <c r="W10" s="43">
-        <v>0</v>
-      </c>
-      <c r="X10" s="43">
-        <f>W10</f>
-      </c>
-      <c r="Y10" s="43">
-        <f>X10</f>
-      </c>
-      <c r="Z10" s="43">
-        <f>Y10</f>
-      </c>
-      <c r="AA10" s="43">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="43">
-        <f>AA10</f>
-      </c>
-      <c r="AC10" s="43">
-        <f>AB10</f>
-      </c>
-      <c r="AD10" s="43">
-        <f>AC10</f>
-      </c>
-      <c r="AE10" s="43">
-        <f>AD10</f>
-      </c>
-      <c r="AF10" s="43">
-        <f>AE10</f>
-      </c>
-      <c r="AG10" s="43">
-        <f>AF10</f>
-      </c>
-      <c r="AH10" s="43">
-        <f>AG10</f>
-      </c>
-      <c r="AI10" s="43">
-        <f>AH10</f>
-      </c>
-      <c r="AJ10" s="43">
-        <f>AI10</f>
-      </c>
-      <c r="AK10" s="43">
-        <f>AJ10</f>
-      </c>
-      <c r="AL10" s="43">
-        <f>AK10</f>
-      </c>
-      <c r="AM10" s="43">
-        <f>AL10</f>
-      </c>
-      <c r="AN10" s="43">
-        <f>AM10</f>
-      </c>
-      <c r="AO10" s="43">
-        <f>AN10</f>
-      </c>
-      <c r="AP10" s="43">
-        <f>AO10</f>
-      </c>
-      <c r="AQ10" s="43">
-        <f>AP10</f>
-      </c>
-      <c r="AR10" s="43">
-        <f>AQ10</f>
-      </c>
-      <c r="AS10" s="43">
-        <f>AR10</f>
-      </c>
-      <c r="AT10" s="43">
-        <f>AS10</f>
-      </c>
-      <c r="AU10" s="43">
-        <f>AT10</f>
-      </c>
-    </row>
-    <row r="11" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A11" s="61">
-        <f>A10</f>
-      </c>
-      <c r="B11" s="41">
-        <v>1</v>
-      </c>
-      <c r="C11" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D11" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="78" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="78" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="43"/>
-      <c r="K11" s="43"/>
-      <c r="L11" s="43">
-        <v>0</v>
-      </c>
-      <c r="M11" s="43">
-        <v>0</v>
-      </c>
-      <c r="N11" s="43">
-        <v>0</v>
-      </c>
-      <c r="O11" s="43">
-        <v>0</v>
-      </c>
-      <c r="P11" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="R11" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="S11" s="43">
-        <f>R11</f>
-      </c>
-      <c r="T11" s="43">
-        <f>S11</f>
-      </c>
-      <c r="U11" s="43">
-        <f>T11</f>
-      </c>
-      <c r="V11" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="W11" s="43">
-        <v>0</v>
-      </c>
-      <c r="X11" s="43">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="43">
-        <f>X11</f>
-      </c>
-      <c r="Z11" s="43">
-        <f>Y11</f>
-      </c>
-      <c r="AA11" s="43">
-        <f>Z11</f>
-      </c>
-      <c r="AB11" s="43">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="43">
-        <f>AB11</f>
-      </c>
-      <c r="AD11" s="43">
-        <f>AC11</f>
-      </c>
-      <c r="AE11" s="43">
-        <f>AD11</f>
-      </c>
-      <c r="AF11" s="43">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="43">
-        <f>AF11</f>
-      </c>
-      <c r="AH11" s="43">
-        <f>AG11</f>
-      </c>
-      <c r="AI11" s="43">
-        <f>AH11</f>
-      </c>
-      <c r="AJ11" s="43">
-        <f>AI11</f>
-      </c>
-      <c r="AK11" s="43">
-        <f>AJ11</f>
-      </c>
-      <c r="AL11" s="43">
-        <f>AK11</f>
-      </c>
-      <c r="AM11" s="43">
-        <f>AL11</f>
-      </c>
-      <c r="AN11" s="43">
-        <f>AM11</f>
-      </c>
-      <c r="AO11" s="43">
-        <f>AN11</f>
-      </c>
-      <c r="AP11" s="43">
-        <f>AO11</f>
-      </c>
-      <c r="AQ11" s="43">
-        <f>AP11</f>
-      </c>
-      <c r="AR11" s="43">
-        <f>AQ11</f>
-      </c>
-      <c r="AS11" s="43">
-        <f>AR11</f>
-      </c>
-      <c r="AT11" s="43">
-        <f>AS11</f>
-      </c>
-      <c r="AU11" s="43">
-        <f>AT11</f>
-      </c>
-    </row>
-    <row r="12" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A12" s="61">
-        <f>A11</f>
-      </c>
-      <c r="B12" s="41">
-        <v>1</v>
-      </c>
-      <c r="C12" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D12" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="78" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="78" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="43">
-        <v>0</v>
-      </c>
-      <c r="M12" s="43">
-        <v>0</v>
-      </c>
-      <c r="N12" s="43">
-        <v>0</v>
-      </c>
-      <c r="O12" s="43">
-        <v>0</v>
-      </c>
-      <c r="P12" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="R12" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="S12" s="43">
-        <f>R12</f>
-      </c>
-      <c r="T12" s="43">
-        <f>S12</f>
-      </c>
-      <c r="U12" s="43">
-        <f>T12</f>
-      </c>
-      <c r="V12" s="43">
-        <f>U12</f>
-      </c>
-      <c r="W12" s="43">
-        <f>V12</f>
-      </c>
-      <c r="X12" s="43">
-        <f>W12</f>
-      </c>
-      <c r="Y12" s="43">
-        <f>X12</f>
-      </c>
-      <c r="Z12" s="43">
-        <f>Y12</f>
-      </c>
-      <c r="AA12" s="43">
-        <f>Z12</f>
-      </c>
-      <c r="AB12" s="43">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="43">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="43">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="43">
-        <f>AD12</f>
-      </c>
-      <c r="AF12" s="43">
-        <f>AE12</f>
-      </c>
-      <c r="AG12" s="43">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="43">
-        <f>AG12</f>
-      </c>
-      <c r="AI12" s="43">
-        <f>AH12</f>
-      </c>
-      <c r="AJ12" s="43">
-        <f>AI12</f>
-      </c>
-      <c r="AK12" s="43">
-        <v>0</v>
-      </c>
-      <c r="AL12" s="43">
-        <f>AK12</f>
-      </c>
-      <c r="AM12" s="43">
-        <f>AL12</f>
-      </c>
-      <c r="AN12" s="43">
-        <f>AM12</f>
-      </c>
-      <c r="AO12" s="43">
-        <f>AN12</f>
-      </c>
-      <c r="AP12" s="43">
-        <f>AO12</f>
-      </c>
-      <c r="AQ12" s="43">
-        <f>AP12</f>
-      </c>
-      <c r="AR12" s="43">
-        <f>AQ12</f>
-      </c>
-      <c r="AS12" s="43">
-        <f>AR12</f>
-      </c>
-      <c r="AT12" s="43">
-        <f>AS12</f>
-      </c>
-      <c r="AU12" s="43">
-        <f>AT12</f>
-      </c>
-    </row>
-    <row r="13" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A13" s="61">
-        <f>A12</f>
-      </c>
-      <c r="B13" s="41">
-        <v>1</v>
-      </c>
-      <c r="C13" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="78" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" s="78" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="43">
-        <v>0</v>
-      </c>
-      <c r="M13" s="43">
-        <v>0</v>
-      </c>
-      <c r="N13" s="43">
-        <v>0</v>
-      </c>
-      <c r="O13" s="43">
-        <v>0</v>
-      </c>
-      <c r="P13" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="R13" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="S13" s="43">
-        <f>R13</f>
-      </c>
-      <c r="T13" s="43">
-        <f>S13</f>
-      </c>
-      <c r="U13" s="43">
-        <f>T13</f>
-      </c>
-      <c r="V13" s="43">
-        <f>U13</f>
-      </c>
-      <c r="W13" s="43">
-        <f>V13</f>
-      </c>
-      <c r="X13" s="43">
-        <f>W13</f>
-      </c>
-      <c r="Y13" s="43">
-        <f>X13</f>
-      </c>
-      <c r="Z13" s="43">
-        <f>Y13</f>
-      </c>
-      <c r="AA13" s="43">
-        <f>Z13</f>
-      </c>
-      <c r="AB13" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="AC13" s="43">
-        <f>AB13</f>
-      </c>
-      <c r="AD13" s="43">
-        <f>AC13</f>
-      </c>
-      <c r="AE13" s="43">
-        <f>AD13</f>
-      </c>
-      <c r="AF13" s="43">
-        <f>AE13</f>
-      </c>
-      <c r="AG13" s="43">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="43">
-        <f>AG13</f>
-      </c>
-      <c r="AI13" s="43">
-        <f>AH13</f>
-      </c>
-      <c r="AJ13" s="43">
-        <f>AI13</f>
-      </c>
-      <c r="AK13" s="43">
-        <f>AJ13</f>
-      </c>
-      <c r="AL13" s="43">
-        <v>0</v>
-      </c>
-      <c r="AM13" s="43">
-        <f>AL13</f>
-      </c>
-      <c r="AN13" s="43">
-        <f>AM13</f>
-      </c>
-      <c r="AO13" s="43">
-        <f>AN13</f>
-      </c>
-      <c r="AP13" s="43">
-        <f>AO13</f>
-      </c>
-      <c r="AQ13" s="43">
-        <f>AP13</f>
-      </c>
-      <c r="AR13" s="43">
-        <f>AQ13</f>
-      </c>
-      <c r="AS13" s="43">
-        <f>AR13</f>
-      </c>
-      <c r="AT13" s="43">
-        <f>AS13</f>
-      </c>
-      <c r="AU13" s="43">
-        <f>AT13</f>
-      </c>
-    </row>
-    <row r="14" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A14" s="61">
-        <f>A13</f>
-      </c>
-      <c r="B14" s="41">
-        <v>1</v>
-      </c>
-      <c r="C14" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D14" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="78" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="43">
-        <v>0</v>
-      </c>
-      <c r="M14" s="43">
-        <v>0</v>
-      </c>
-      <c r="N14" s="43">
-        <v>0</v>
-      </c>
-      <c r="O14" s="43">
-        <v>0</v>
-      </c>
-      <c r="P14" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="R14" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="S14" s="43">
-        <f>R14</f>
-      </c>
-      <c r="T14" s="43">
-        <f>S14</f>
-      </c>
-      <c r="U14" s="43">
-        <f>T14</f>
-      </c>
-      <c r="V14" s="43">
-        <f>U14</f>
-      </c>
-      <c r="W14" s="43">
-        <f>V14</f>
-      </c>
-      <c r="X14" s="43">
-        <f>W14</f>
-      </c>
-      <c r="Y14" s="43">
-        <f>X14</f>
-      </c>
-      <c r="Z14" s="43">
-        <f>Y14</f>
-      </c>
-      <c r="AA14" s="43">
-        <f>Z14</f>
-      </c>
-      <c r="AB14" s="43">
-        <f>AA14</f>
-      </c>
-      <c r="AC14" s="43">
-        <f>AB14</f>
-      </c>
-      <c r="AD14" s="43">
-        <f>AC14</f>
-      </c>
-      <c r="AE14" s="43">
-        <f>AD14</f>
-      </c>
-      <c r="AF14" s="43">
-        <f>AE14</f>
-      </c>
-      <c r="AG14" s="43">
-        <f>AF14</f>
-      </c>
-      <c r="AH14" s="43">
-        <f>AG14</f>
-      </c>
-      <c r="AI14" s="43">
-        <f>AH14</f>
-      </c>
-      <c r="AJ14" s="43">
-        <f>AI14</f>
-      </c>
-      <c r="AK14" s="43">
-        <f>AJ14</f>
-      </c>
-      <c r="AL14" s="43">
-        <v>0</v>
-      </c>
-      <c r="AM14" s="43">
-        <f>AL14</f>
-      </c>
-      <c r="AN14" s="43">
-        <f>AM14</f>
-      </c>
-      <c r="AO14" s="43">
-        <f>AN14</f>
-      </c>
-      <c r="AP14" s="43">
-        <f>AO14</f>
-      </c>
-      <c r="AQ14" s="43">
-        <v>0</v>
-      </c>
-      <c r="AR14" s="43">
-        <f>AQ14</f>
-      </c>
-      <c r="AS14" s="43">
-        <f>AR14</f>
-      </c>
-      <c r="AT14" s="43">
-        <f>AS14</f>
-      </c>
-      <c r="AU14" s="43">
-        <f>AT14</f>
-      </c>
-    </row>
-    <row r="15" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A15" s="61">
-        <f>A9</f>
-      </c>
-      <c r="B15" s="41">
-        <v>1</v>
-      </c>
-      <c r="C15" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D15" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="78" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="78" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43">
-        <v>0</v>
-      </c>
-      <c r="M15" s="43">
-        <v>0</v>
-      </c>
-      <c r="N15" s="43">
-        <v>0</v>
-      </c>
-      <c r="O15" s="43">
-        <v>0</v>
-      </c>
-      <c r="P15" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="R15" s="43">
-        <f>Q15</f>
-      </c>
-      <c r="S15" s="43">
-        <f>R15</f>
-      </c>
-      <c r="T15" s="43">
-        <f>S15</f>
-      </c>
-      <c r="U15" s="43">
-        <f>T15</f>
-      </c>
-      <c r="V15" s="43">
-        <f>U15</f>
-      </c>
-      <c r="W15" s="43">
-        <f>V15</f>
-      </c>
-      <c r="X15" s="43">
-        <f>W15</f>
-      </c>
-      <c r="Y15" s="43">
-        <f>X15</f>
-      </c>
-      <c r="Z15" s="43">
-        <f>Y15</f>
-      </c>
-      <c r="AA15" s="43">
-        <f>Z15</f>
-      </c>
-      <c r="AB15" s="43">
-        <f>AA15</f>
-      </c>
-      <c r="AC15" s="43">
-        <f>AB15</f>
-      </c>
-      <c r="AD15" s="43">
-        <f>AC15</f>
-      </c>
-      <c r="AE15" s="43">
-        <f>AD15</f>
-      </c>
-      <c r="AF15" s="43">
-        <f>AE15</f>
-      </c>
-      <c r="AG15" s="43">
-        <f>AF15</f>
-      </c>
-      <c r="AH15" s="43">
-        <f>AG15</f>
-      </c>
-      <c r="AI15" s="43">
-        <f>AH15</f>
-      </c>
-      <c r="AJ15" s="43">
-        <f>AI15</f>
-      </c>
-      <c r="AK15" s="43">
-        <f>AJ15</f>
-      </c>
-      <c r="AL15" s="43">
-        <f>AK15</f>
-      </c>
-      <c r="AM15" s="43">
-        <f>AL15</f>
-      </c>
-      <c r="AN15" s="43">
-        <f>AM15</f>
-      </c>
-      <c r="AO15" s="43">
-        <f>AN15</f>
-      </c>
-      <c r="AP15" s="43">
-        <f>AO15</f>
-      </c>
-      <c r="AQ15" s="43">
-        <f>AP15</f>
-      </c>
-      <c r="AR15" s="43">
-        <f>AQ15</f>
-      </c>
-      <c r="AS15" s="43">
-        <f>AR15</f>
-      </c>
-      <c r="AT15" s="43">
-        <f>AS15</f>
-      </c>
-      <c r="AU15" s="43">
-        <f>AT15</f>
-      </c>
-    </row>
-    <row r="16" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A16" s="79">
-        <f>A10</f>
-      </c>
-      <c r="B16" s="49">
-        <v>1</v>
-      </c>
-      <c r="C16" s="49" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16" s="49" t="s">
-        <v>4</v>
-      </c>
-      <c r="E16" s="80" t="s">
-        <v>24</v>
-      </c>
-      <c r="F16" s="80" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
-      <c r="K16" s="51"/>
-      <c r="L16" s="51">
-        <v>0</v>
-      </c>
-      <c r="M16" s="51">
-        <f>L16</f>
-      </c>
-      <c r="N16" s="51">
-        <f>M16</f>
-      </c>
-      <c r="O16" s="51">
-        <f>N16</f>
-      </c>
-      <c r="P16" s="51">
-        <f>O16</f>
-      </c>
-      <c r="Q16" s="51">
-        <f>P16</f>
-      </c>
-      <c r="R16" s="51">
-        <f>Q16</f>
-      </c>
-      <c r="S16" s="51">
-        <f>R16</f>
-      </c>
-      <c r="T16" s="51">
-        <f>S16</f>
-      </c>
-      <c r="U16" s="51">
-        <f>T16</f>
-      </c>
-      <c r="V16" s="51">
-        <f>U16</f>
-      </c>
-      <c r="W16" s="51">
-        <f>V16</f>
-      </c>
-      <c r="X16" s="51">
-        <f>W16</f>
-      </c>
-      <c r="Y16" s="51">
-        <f>X16</f>
-      </c>
-      <c r="Z16" s="51">
-        <f>Y16</f>
-      </c>
-      <c r="AA16" s="51">
-        <f>Z16</f>
-      </c>
-      <c r="AB16" s="51">
-        <f>AA16</f>
-      </c>
-      <c r="AC16" s="51">
-        <f>AB16</f>
-      </c>
-      <c r="AD16" s="51">
-        <f>AC16</f>
-      </c>
-      <c r="AE16" s="51">
-        <f>AD16</f>
-      </c>
-      <c r="AF16" s="51">
-        <f>AE16</f>
-      </c>
-      <c r="AG16" s="51">
-        <f>AF16</f>
-      </c>
-      <c r="AH16" s="51">
-        <f>AG16</f>
-      </c>
-      <c r="AI16" s="51">
-        <f>AH16</f>
-      </c>
-      <c r="AJ16" s="51">
-        <f>AI16</f>
-      </c>
-      <c r="AK16" s="51">
-        <f>AJ16</f>
-      </c>
-      <c r="AL16" s="51">
-        <f>AK16</f>
-      </c>
-      <c r="AM16" s="51">
-        <f>AL16</f>
-      </c>
-      <c r="AN16" s="51">
-        <f>AM16</f>
-      </c>
-      <c r="AO16" s="51">
-        <f>AN16</f>
-      </c>
-      <c r="AP16" s="51">
-        <f>AO16</f>
-      </c>
-      <c r="AQ16" s="51">
-        <f>AP16</f>
-      </c>
-      <c r="AR16" s="51">
-        <f>AQ16</f>
-      </c>
-      <c r="AS16" s="51">
-        <f>AR16</f>
-      </c>
-      <c r="AT16" s="51">
-        <f>AS16</f>
-      </c>
-      <c r="AU16" s="51">
-        <f>AT16</f>
-      </c>
-    </row>
-    <row r="17" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A17" s="61">
-        <f>A12</f>
-      </c>
-      <c r="B17" s="41">
-        <v>1</v>
-      </c>
-      <c r="C17" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D17" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="78" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="78" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="43"/>
-      <c r="L17" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="M17" s="43">
-        <f>L17</f>
-      </c>
-      <c r="N17" s="43">
-        <f>M17</f>
-      </c>
-      <c r="O17" s="43">
-        <f>N17</f>
-      </c>
-      <c r="P17" s="43">
-        <f>O17</f>
-      </c>
-      <c r="Q17" s="43">
-        <f>P17</f>
-      </c>
-      <c r="R17" s="43">
-        <f>Q17</f>
-      </c>
-      <c r="S17" s="43">
-        <f>R17</f>
-      </c>
-      <c r="T17" s="43">
-        <f>S17</f>
-      </c>
-      <c r="U17" s="43">
-        <f>T17</f>
-      </c>
-      <c r="V17" s="43">
-        <f>U17</f>
-      </c>
-      <c r="W17" s="43">
-        <f>V17</f>
-      </c>
-      <c r="X17" s="43">
-        <f>W17</f>
-      </c>
-      <c r="Y17" s="43">
-        <f>X17</f>
-      </c>
-      <c r="Z17" s="43">
-        <f>Y17</f>
-      </c>
-      <c r="AA17" s="43">
-        <f>Z17</f>
-      </c>
-      <c r="AB17" s="43">
-        <f>AA17</f>
-      </c>
-      <c r="AC17" s="43">
-        <f>AB17</f>
-      </c>
-      <c r="AD17" s="43">
-        <f>AC17</f>
-      </c>
-      <c r="AE17" s="43">
-        <f>AD17</f>
-      </c>
-      <c r="AF17" s="43">
-        <f>AE17</f>
-      </c>
-      <c r="AG17" s="43">
-        <f>AF17</f>
-      </c>
-      <c r="AH17" s="43">
-        <f>AG17</f>
-      </c>
-      <c r="AI17" s="43">
-        <f>AH17</f>
-      </c>
-      <c r="AJ17" s="43">
-        <f>AI17</f>
-      </c>
-      <c r="AK17" s="43">
-        <f>AJ17</f>
-      </c>
-      <c r="AL17" s="43">
-        <f>AK17</f>
-      </c>
-      <c r="AM17" s="43">
-        <f>AL17</f>
-      </c>
-      <c r="AN17" s="43">
-        <f>AM17</f>
-      </c>
-      <c r="AO17" s="43">
-        <f>AN17</f>
-      </c>
-      <c r="AP17" s="43">
-        <f>AO17</f>
-      </c>
-      <c r="AQ17" s="43">
-        <f>AP17</f>
-      </c>
-      <c r="AR17" s="43">
-        <f>AQ17</f>
-      </c>
-      <c r="AS17" s="43">
-        <f>AR17</f>
-      </c>
-      <c r="AT17" s="43">
-        <f>AS17</f>
-      </c>
-      <c r="AU17" s="43">
-        <f>AT17</f>
-      </c>
-    </row>
-    <row r="18" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A18" s="61">
-        <f>A17</f>
-      </c>
-      <c r="B18" s="41">
-        <v>1</v>
-      </c>
-      <c r="C18" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" s="49" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="78" t="s">
-        <v>26</v>
-      </c>
-      <c r="F18" s="78" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="M18" s="43">
-        <f>L18</f>
-      </c>
-      <c r="N18" s="43">
-        <f>M18</f>
-      </c>
-      <c r="O18" s="43">
-        <f>N18</f>
-      </c>
-      <c r="P18" s="43">
-        <f>O18</f>
-      </c>
-      <c r="Q18" s="43">
-        <f>P18</f>
-      </c>
-      <c r="R18" s="43">
-        <f>Q18</f>
-      </c>
-      <c r="S18" s="43">
-        <f>R18</f>
-      </c>
-      <c r="T18" s="43">
-        <f>S18</f>
-      </c>
-      <c r="U18" s="43">
-        <f>T18</f>
-      </c>
-      <c r="V18" s="43">
-        <f>U18</f>
-      </c>
-      <c r="W18" s="43">
-        <f>V18</f>
-      </c>
-      <c r="X18" s="43">
-        <f>W18</f>
-      </c>
-      <c r="Y18" s="43">
-        <f>X18</f>
-      </c>
-      <c r="Z18" s="43">
-        <f>Y18</f>
-      </c>
-      <c r="AA18" s="43">
-        <f>Z18</f>
-      </c>
-      <c r="AB18" s="43">
-        <f>AA18</f>
-      </c>
-      <c r="AC18" s="43">
-        <f>AB18</f>
-      </c>
-      <c r="AD18" s="43">
-        <f>AC18</f>
-      </c>
-      <c r="AE18" s="43">
-        <f>AD18</f>
-      </c>
-      <c r="AF18" s="43">
-        <f>AE18</f>
-      </c>
-      <c r="AG18" s="43">
-        <f>AF18</f>
-      </c>
-      <c r="AH18" s="43">
-        <f>AG18</f>
-      </c>
-      <c r="AI18" s="43">
-        <f>AH18</f>
-      </c>
-      <c r="AJ18" s="43">
-        <f>AI18</f>
-      </c>
-      <c r="AK18" s="43">
-        <f>AJ18</f>
-      </c>
-      <c r="AL18" s="43">
-        <f>AK18</f>
-      </c>
-      <c r="AM18" s="43">
-        <f>AL18</f>
-      </c>
-      <c r="AN18" s="43">
-        <f>AM18</f>
-      </c>
-      <c r="AO18" s="43">
-        <f>AN18</f>
-      </c>
-      <c r="AP18" s="43">
-        <f>AO18</f>
-      </c>
-      <c r="AQ18" s="43">
-        <f>AP18</f>
-      </c>
-      <c r="AR18" s="43">
-        <f>AQ18</f>
-      </c>
-      <c r="AS18" s="43">
-        <f>AR18</f>
-      </c>
-      <c r="AT18" s="43">
-        <f>AS18</f>
-      </c>
-      <c r="AU18" s="43">
-        <f>AT18</f>
-      </c>
-    </row>
-    <row r="19" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A19" s="61">
-        <f>A18</f>
-      </c>
-      <c r="B19" s="41">
-        <v>1</v>
-      </c>
-      <c r="C19" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="78" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" s="78" t="s">
-        <v>29</v>
-      </c>
-      <c r="G19" s="43"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
-      <c r="L19" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="M19" s="43">
-        <f>L19</f>
-      </c>
-      <c r="N19" s="43">
-        <f>M19</f>
-      </c>
-      <c r="O19" s="43">
-        <f>N19</f>
-      </c>
-      <c r="P19" s="43">
-        <f>O19</f>
-      </c>
-      <c r="Q19" s="43">
-        <f>P19</f>
-      </c>
-      <c r="R19" s="43">
-        <f>Q19</f>
-      </c>
-      <c r="S19" s="43">
-        <f>R19</f>
-      </c>
-      <c r="T19" s="43">
-        <f>S19</f>
-      </c>
-      <c r="U19" s="43">
-        <f>T19</f>
-      </c>
-      <c r="V19" s="43">
-        <f>U19</f>
-      </c>
-      <c r="W19" s="43">
-        <f>V19</f>
-      </c>
-      <c r="X19" s="43">
-        <f>W19</f>
-      </c>
-      <c r="Y19" s="43">
-        <f>X19</f>
-      </c>
-      <c r="Z19" s="43">
-        <f>Y19</f>
-      </c>
-      <c r="AA19" s="43">
-        <f>Z19</f>
-      </c>
-      <c r="AB19" s="43">
-        <f>AA19</f>
-      </c>
-      <c r="AC19" s="43">
-        <f>AB19</f>
-      </c>
-      <c r="AD19" s="43">
-        <f>AC19</f>
-      </c>
-      <c r="AE19" s="43">
-        <f>AD19</f>
-      </c>
-      <c r="AF19" s="43">
-        <f>AE19</f>
-      </c>
-      <c r="AG19" s="43">
-        <f>AF19</f>
-      </c>
-      <c r="AH19" s="43">
-        <f>AG19</f>
-      </c>
-      <c r="AI19" s="43">
-        <f>AH19</f>
-      </c>
-      <c r="AJ19" s="43">
-        <f>AI19</f>
-      </c>
-      <c r="AK19" s="43">
-        <f>AJ19</f>
-      </c>
-      <c r="AL19" s="43">
-        <f>AK19</f>
-      </c>
-      <c r="AM19" s="43">
-        <f>AL19</f>
-      </c>
-      <c r="AN19" s="43">
-        <f>AM19</f>
-      </c>
-      <c r="AO19" s="43">
-        <f>AN19</f>
-      </c>
-      <c r="AP19" s="43">
-        <f>AO19</f>
-      </c>
-      <c r="AQ19" s="43">
-        <f>AP19</f>
-      </c>
-      <c r="AR19" s="43">
-        <f>AQ19</f>
-      </c>
-      <c r="AS19" s="43">
-        <f>AR19</f>
-      </c>
-      <c r="AT19" s="43">
-        <f>AS19</f>
-      </c>
-      <c r="AU19" s="43">
-        <f>AT19</f>
-      </c>
-    </row>
-    <row r="20" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A20" s="61">
-        <f>A19</f>
-      </c>
-      <c r="B20" s="41">
-        <v>1</v>
-      </c>
-      <c r="C20" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D20" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="78" t="s">
-        <v>30</v>
-      </c>
-      <c r="F20" s="78" t="s">
-        <v>29</v>
-      </c>
-      <c r="G20" s="43"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="M20" s="43">
-        <f>L20</f>
-      </c>
-      <c r="N20" s="43">
-        <f>M20</f>
-      </c>
-      <c r="O20" s="43">
-        <f>N20</f>
-      </c>
-      <c r="P20" s="43">
-        <f>O20</f>
-      </c>
-      <c r="Q20" s="43">
-        <f>P20</f>
-      </c>
-      <c r="R20" s="43">
-        <f>Q20</f>
-      </c>
-      <c r="S20" s="43">
-        <f>R20</f>
-      </c>
-      <c r="T20" s="43">
-        <f>S20</f>
-      </c>
-      <c r="U20" s="43">
-        <f>T20</f>
-      </c>
-      <c r="V20" s="43">
-        <f>U20</f>
-      </c>
-      <c r="W20" s="43">
-        <f>V20</f>
-      </c>
-      <c r="X20" s="43">
-        <f>W20</f>
-      </c>
-      <c r="Y20" s="43">
-        <f>X20</f>
-      </c>
-      <c r="Z20" s="43">
-        <f>Y20</f>
-      </c>
-      <c r="AA20" s="43">
-        <f>Z20</f>
-      </c>
-      <c r="AB20" s="43">
-        <f>AA20</f>
-      </c>
-      <c r="AC20" s="43">
-        <f>AB20</f>
-      </c>
-      <c r="AD20" s="43">
-        <f>AC20</f>
-      </c>
-      <c r="AE20" s="43">
-        <f>AD20</f>
-      </c>
-      <c r="AF20" s="43">
-        <f>AE20</f>
-      </c>
-      <c r="AG20" s="43">
-        <f>AF20</f>
-      </c>
-      <c r="AH20" s="43">
-        <f>AG20</f>
-      </c>
-      <c r="AI20" s="43">
-        <f>AH20</f>
-      </c>
-      <c r="AJ20" s="43">
-        <f>AI20</f>
-      </c>
-      <c r="AK20" s="43">
-        <f>AJ20</f>
-      </c>
-      <c r="AL20" s="43">
-        <f>AK20</f>
-      </c>
-      <c r="AM20" s="43">
-        <f>AL20</f>
-      </c>
-      <c r="AN20" s="43">
-        <f>AM20</f>
-      </c>
-      <c r="AO20" s="43">
-        <f>AN20</f>
-      </c>
-      <c r="AP20" s="43">
-        <f>AO20</f>
-      </c>
-      <c r="AQ20" s="43">
-        <f>AP20</f>
-      </c>
-      <c r="AR20" s="43">
-        <f>AQ20</f>
-      </c>
-      <c r="AS20" s="43">
-        <f>AR20</f>
-      </c>
-      <c r="AT20" s="43">
-        <f>AS20</f>
-      </c>
-      <c r="AU20" s="43">
-        <f>AT20</f>
-      </c>
-    </row>
-    <row r="21" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A21" s="61">
-        <f>A20</f>
-      </c>
-      <c r="B21" s="41">
-        <v>1</v>
-      </c>
-      <c r="C21" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="78" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="78" t="s">
-        <v>29</v>
-      </c>
-      <c r="G21" s="43"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="M21" s="43">
-        <f>L21</f>
-      </c>
-      <c r="N21" s="43">
-        <f>M21</f>
-      </c>
-      <c r="O21" s="43">
-        <f>N21</f>
-      </c>
-      <c r="P21" s="43">
-        <f>O21</f>
-      </c>
-      <c r="Q21" s="43">
-        <f>P21</f>
-      </c>
-      <c r="R21" s="43">
-        <f>Q21</f>
-      </c>
-      <c r="S21" s="43">
-        <f>R21</f>
-      </c>
-      <c r="T21" s="43">
-        <f>S21</f>
-      </c>
-      <c r="U21" s="43">
-        <f>T21</f>
-      </c>
-      <c r="V21" s="43">
-        <f>U21</f>
-      </c>
-      <c r="W21" s="43">
-        <f>V21</f>
-      </c>
-      <c r="X21" s="43">
-        <f>W21</f>
-      </c>
-      <c r="Y21" s="43">
-        <f>X21</f>
-      </c>
-      <c r="Z21" s="43">
-        <f>Y21</f>
-      </c>
-      <c r="AA21" s="43">
-        <f>Z21</f>
-      </c>
-      <c r="AB21" s="43">
-        <f>AA21</f>
-      </c>
-      <c r="AC21" s="43">
-        <f>AB21</f>
-      </c>
-      <c r="AD21" s="43">
-        <f>AC21</f>
-      </c>
-      <c r="AE21" s="43">
-        <f>AD21</f>
-      </c>
-      <c r="AF21" s="43">
-        <f>AE21</f>
-      </c>
-      <c r="AG21" s="43">
-        <f>AF21</f>
-      </c>
-      <c r="AH21" s="43">
-        <f>AG21</f>
-      </c>
-      <c r="AI21" s="43">
-        <f>AH21</f>
-      </c>
-      <c r="AJ21" s="43">
-        <f>AI21</f>
-      </c>
-      <c r="AK21" s="43">
-        <f>AJ21</f>
-      </c>
-      <c r="AL21" s="43">
-        <f>AK21</f>
-      </c>
-      <c r="AM21" s="43">
-        <f>AL21</f>
-      </c>
-      <c r="AN21" s="43">
-        <f>AM21</f>
-      </c>
-      <c r="AO21" s="43">
-        <f>AN21</f>
-      </c>
-      <c r="AP21" s="43">
-        <f>AO21</f>
-      </c>
-      <c r="AQ21" s="43">
-        <f>AP21</f>
-      </c>
-      <c r="AR21" s="43">
-        <f>AQ21</f>
-      </c>
-      <c r="AS21" s="43">
-        <f>AR21</f>
-      </c>
-      <c r="AT21" s="43">
-        <f>AS21</f>
-      </c>
-      <c r="AU21" s="43">
-        <f>AT21</f>
-      </c>
-    </row>
-    <row r="22" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A22" s="61">
-        <f>A21</f>
-      </c>
-      <c r="B22" s="41">
-        <v>1</v>
-      </c>
-      <c r="C22" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="80" t="s">
-        <v>33</v>
-      </c>
-      <c r="F22" s="78" t="s">
-        <v>29</v>
-      </c>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="M22" s="43">
-        <f>L22</f>
-      </c>
-      <c r="N22" s="43">
-        <f>M22</f>
-      </c>
-      <c r="O22" s="43">
-        <f>N22</f>
-      </c>
-      <c r="P22" s="43">
-        <f>O22</f>
-      </c>
-      <c r="Q22" s="43">
-        <f>P22</f>
-      </c>
-      <c r="R22" s="43">
-        <f>Q22</f>
-      </c>
-      <c r="S22" s="43">
-        <f>R22</f>
-      </c>
-      <c r="T22" s="43">
-        <f>S22</f>
-      </c>
-      <c r="U22" s="43">
-        <f>T22</f>
-      </c>
-      <c r="V22" s="43">
-        <f>U22</f>
-      </c>
-      <c r="W22" s="43">
-        <f>V22</f>
-      </c>
-      <c r="X22" s="43">
-        <f>W22</f>
-      </c>
-      <c r="Y22" s="43">
-        <f>X22</f>
-      </c>
-      <c r="Z22" s="43">
-        <f>Y22</f>
-      </c>
-      <c r="AA22" s="43">
-        <f>Z22</f>
-      </c>
-      <c r="AB22" s="43">
-        <f>AA22</f>
-      </c>
-      <c r="AC22" s="43">
-        <f>AB22</f>
-      </c>
-      <c r="AD22" s="43">
-        <f>AC22</f>
-      </c>
-      <c r="AE22" s="43">
-        <f>AD22</f>
-      </c>
-      <c r="AF22" s="43">
-        <f>AE22</f>
-      </c>
-      <c r="AG22" s="43">
-        <f>AF22</f>
-      </c>
-      <c r="AH22" s="43">
-        <f>AG22</f>
-      </c>
-      <c r="AI22" s="43">
-        <f>AH22</f>
-      </c>
-      <c r="AJ22" s="43">
-        <f>AI22</f>
-      </c>
-      <c r="AK22" s="43">
-        <f>AJ22</f>
-      </c>
-      <c r="AL22" s="43">
-        <f>AK22</f>
-      </c>
-      <c r="AM22" s="43">
-        <f>AL22</f>
-      </c>
-      <c r="AN22" s="43">
-        <f>AM22</f>
-      </c>
-      <c r="AO22" s="43">
-        <f>AN22</f>
-      </c>
-      <c r="AP22" s="43">
-        <f>AO22</f>
-      </c>
-      <c r="AQ22" s="43">
-        <f>AP22</f>
-      </c>
-      <c r="AR22" s="43">
-        <f>AQ22</f>
-      </c>
-      <c r="AS22" s="43">
-        <f>AR22</f>
-      </c>
-      <c r="AT22" s="43">
-        <f>AS22</f>
-      </c>
-      <c r="AU22" s="43">
-        <f>AT22</f>
-      </c>
-    </row>
-    <row r="23" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A23" s="81" t="s">
-        <v>111</v>
-      </c>
-      <c r="B23" s="82">
-        <v>1</v>
-      </c>
-      <c r="C23" s="82" t="s">
-        <v>94</v>
-      </c>
-      <c r="D23" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" s="81" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="81" t="s">
-        <v>6</v>
-      </c>
-      <c r="G23" s="43"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="43"/>
-      <c r="J23" s="43"/>
-      <c r="K23" s="43"/>
-      <c r="L23" s="83">
-        <f>L6</f>
-      </c>
-      <c r="M23" s="83">
-        <f>L23+M6</f>
-      </c>
-      <c r="N23" s="83">
-        <f>M23+N6</f>
-      </c>
-      <c r="O23" s="83">
-        <f>N23+O6</f>
-      </c>
-      <c r="P23" s="83">
-        <f>O23+P6</f>
-      </c>
-      <c r="Q23" s="83">
-        <f>P23+Q6</f>
-      </c>
-      <c r="R23" s="83">
-        <f>Q23+R6</f>
-      </c>
-      <c r="S23" s="83">
-        <f>R23+S6</f>
-      </c>
-      <c r="T23" s="83">
-        <f>S23+T6</f>
-      </c>
-      <c r="U23" s="83">
-        <f>T23+U6</f>
-      </c>
-      <c r="V23" s="83">
-        <f>U23+V6</f>
-      </c>
-      <c r="W23" s="83">
-        <f>V23+W6</f>
-      </c>
-      <c r="X23" s="83">
-        <f>W23+X6</f>
-      </c>
-      <c r="Y23" s="83">
-        <f>X23+Y6</f>
-      </c>
-      <c r="Z23" s="83">
-        <f>Y23+Z6</f>
-      </c>
-      <c r="AA23" s="83">
-        <f>Z23+AA6</f>
-      </c>
-      <c r="AB23" s="83">
-        <f>AA23+AB6</f>
-      </c>
-      <c r="AC23" s="83">
-        <f>AB23+AC6</f>
-      </c>
-      <c r="AD23" s="83">
-        <f>AC23+AD6</f>
-      </c>
-      <c r="AE23" s="83">
-        <f>AD23+AE6</f>
-      </c>
-      <c r="AF23" s="83">
-        <f>AE23+AF6</f>
-      </c>
-      <c r="AG23" s="83">
-        <f>AF23+AG6</f>
-      </c>
-      <c r="AH23" s="83">
-        <f>AG23+AH6</f>
-      </c>
-      <c r="AI23" s="83">
-        <f>AH23+AI6</f>
-      </c>
-      <c r="AJ23" s="83">
-        <f>AI23+AJ6</f>
-      </c>
-      <c r="AK23" s="83">
-        <f>AJ23+AK6</f>
-      </c>
-      <c r="AL23" s="83">
-        <f>AK23+AL6</f>
-      </c>
-      <c r="AM23" s="83">
-        <f>AL23+AM6</f>
-      </c>
-      <c r="AN23" s="83">
-        <f>AM23+AN6</f>
-      </c>
-      <c r="AO23" s="83">
-        <f>AN23+AO6</f>
-      </c>
-      <c r="AP23" s="83">
-        <f>AO23+AP6</f>
-      </c>
-      <c r="AQ23" s="83">
-        <f>AP23+AQ6</f>
-      </c>
-      <c r="AR23" s="83">
-        <f>AQ23+AR6</f>
-      </c>
-      <c r="AS23" s="83">
-        <f>AR23+AS6</f>
-      </c>
-      <c r="AT23" s="83">
-        <f>AS23+AT6</f>
-      </c>
-      <c r="AU23" s="83">
-        <f>AT23+AU6</f>
-      </c>
-    </row>
-    <row r="24" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A24" s="81" t="s">
-        <v>112</v>
-      </c>
-      <c r="B24" s="82">
-        <v>1</v>
-      </c>
-      <c r="C24" s="82" t="s">
-        <v>94</v>
-      </c>
-      <c r="D24" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" s="81" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="81" t="s">
-        <v>6</v>
-      </c>
-      <c r="G24" s="43"/>
-      <c r="H24" s="43"/>
-      <c r="I24" s="43"/>
-      <c r="J24" s="43"/>
-      <c r="K24" s="43"/>
-      <c r="L24" s="83">
-        <f>L7</f>
-      </c>
-      <c r="M24" s="83">
-        <f>L24+M7</f>
-      </c>
-      <c r="N24" s="83">
-        <f>M24+N7</f>
-      </c>
-      <c r="O24" s="83">
-        <f>N24+O7</f>
-      </c>
-      <c r="P24" s="83">
-        <f>O24+P7</f>
-      </c>
-      <c r="Q24" s="83">
-        <f>P24+Q7</f>
-      </c>
-      <c r="R24" s="83">
-        <f>Q24+R7</f>
-      </c>
-      <c r="S24" s="83">
-        <f>R24+S7</f>
-      </c>
-      <c r="T24" s="83">
-        <f>S24+T7</f>
-      </c>
-      <c r="U24" s="83">
-        <f>T24+U7</f>
-      </c>
-      <c r="V24" s="83">
-        <f>U24+V7</f>
-      </c>
-      <c r="W24" s="83">
-        <f>V24+W7</f>
-      </c>
-      <c r="X24" s="83">
-        <f>W24+X7</f>
-      </c>
-      <c r="Y24" s="83">
-        <f>X24+Y7</f>
-      </c>
-      <c r="Z24" s="83">
-        <f>Y24+Z7</f>
-      </c>
-      <c r="AA24" s="83">
-        <f>Z24+AA7</f>
-      </c>
-      <c r="AB24" s="83">
-        <f>AA24+AB7</f>
-      </c>
-      <c r="AC24" s="83">
-        <f>AB24+AC7</f>
-      </c>
-      <c r="AD24" s="83">
-        <f>AC24+AD7</f>
-      </c>
-      <c r="AE24" s="83">
-        <f>AD24+AE7</f>
-      </c>
-      <c r="AF24" s="83">
-        <f>AE24+AF7</f>
-      </c>
-      <c r="AG24" s="83">
-        <f>AF24+AG7</f>
-      </c>
-      <c r="AH24" s="83">
-        <f>AG24+AH7</f>
-      </c>
-      <c r="AI24" s="83">
-        <f>AH24+AI7</f>
-      </c>
-      <c r="AJ24" s="83">
-        <f>AI24+AJ7</f>
-      </c>
-      <c r="AK24" s="83">
-        <f>AJ24+AK7</f>
-      </c>
-      <c r="AL24" s="83">
-        <f>AK24+AL7</f>
-      </c>
-      <c r="AM24" s="83">
-        <f>AL24+AM7</f>
-      </c>
-      <c r="AN24" s="83">
-        <f>AM24+AN7</f>
-      </c>
-      <c r="AO24" s="83">
-        <f>AN24+AO7</f>
-      </c>
-      <c r="AP24" s="83">
-        <f>AO24+AP7</f>
-      </c>
-      <c r="AQ24" s="83">
-        <f>AP24+AQ7</f>
-      </c>
-      <c r="AR24" s="83">
-        <f>AQ24+AR7</f>
-      </c>
-      <c r="AS24" s="83">
-        <f>AR24+AS7</f>
-      </c>
-      <c r="AT24" s="83">
-        <f>AS24+AT7</f>
-      </c>
-      <c r="AU24" s="83">
-        <f>AT24+AU7</f>
-      </c>
-    </row>
-    <row r="25" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A25" s="81" t="s">
-        <v>113</v>
-      </c>
-      <c r="B25" s="82">
-        <v>1</v>
-      </c>
-      <c r="C25" s="82" t="s">
-        <v>94</v>
-      </c>
-      <c r="D25" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="E25" s="81" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="81" t="s">
-        <v>6</v>
-      </c>
-      <c r="G25" s="43"/>
-      <c r="H25" s="43"/>
-      <c r="I25" s="43"/>
-      <c r="J25" s="43"/>
-      <c r="K25" s="43"/>
-      <c r="L25" s="83">
-        <f>L23+L24</f>
-      </c>
-      <c r="M25" s="83">
-        <f>M23+M24</f>
-      </c>
-      <c r="N25" s="83">
-        <f>N23+N24</f>
-      </c>
-      <c r="O25" s="83">
-        <f>O23+O24</f>
-      </c>
-      <c r="P25" s="83">
-        <f>P23+P24</f>
-      </c>
-      <c r="Q25" s="83">
-        <f>Q23+Q24</f>
-      </c>
-      <c r="R25" s="83">
-        <f>R23+R24</f>
-      </c>
-      <c r="S25" s="83">
-        <f>S23+S24</f>
-      </c>
-      <c r="T25" s="83">
-        <f>T23+T24</f>
-      </c>
-      <c r="U25" s="83">
-        <f>U23+U24</f>
-      </c>
-      <c r="V25" s="83">
-        <f>V23+V24</f>
-      </c>
-      <c r="W25" s="83">
-        <f>W23+W24</f>
-      </c>
-      <c r="X25" s="83">
-        <f>X23+X24</f>
-      </c>
-      <c r="Y25" s="83">
-        <f>Y23+Y24</f>
-      </c>
-      <c r="Z25" s="83">
-        <f>Z23+Z24</f>
-      </c>
-      <c r="AA25" s="83">
-        <f>AA23+AA24</f>
-      </c>
-      <c r="AB25" s="83">
-        <f>AB23+AB24</f>
-      </c>
-      <c r="AC25" s="83">
-        <f>AC23+AC24</f>
-      </c>
-      <c r="AD25" s="83">
-        <f>AD23+AD24</f>
-      </c>
-      <c r="AE25" s="83">
-        <f>AE23+AE24</f>
-      </c>
-      <c r="AF25" s="83">
-        <f>AF23+AF24</f>
-      </c>
-      <c r="AG25" s="83">
-        <f>AG23+AG24</f>
-      </c>
-      <c r="AH25" s="83">
-        <f>AH23+AH24</f>
-      </c>
-      <c r="AI25" s="83">
-        <f>AI23+AI24</f>
-      </c>
-      <c r="AJ25" s="83">
-        <f>AJ23+AJ24</f>
-      </c>
-      <c r="AK25" s="83">
-        <f>AK23+AK24</f>
-      </c>
-      <c r="AL25" s="83">
-        <f>AL23+AL24</f>
-      </c>
-      <c r="AM25" s="83">
-        <f>AM23+AM24</f>
-      </c>
-      <c r="AN25" s="83">
-        <f>AN23+AN24</f>
-      </c>
-      <c r="AO25" s="83">
-        <f>AO23+AO24</f>
-      </c>
-      <c r="AP25" s="83">
-        <f>AP23+AP24</f>
-      </c>
-      <c r="AQ25" s="83">
-        <f>AQ23+AQ24</f>
-      </c>
-      <c r="AR25" s="83">
-        <f>AR23+AR24</f>
-      </c>
-      <c r="AS25" s="83">
-        <f>AS23+AS24</f>
-      </c>
-      <c r="AT25" s="83">
-        <f>AT23+AT24</f>
-      </c>
-      <c r="AU25" s="83">
-        <f>AU23+AU24</f>
-      </c>
-    </row>
-    <row r="26" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A26" s="47" t="s">
-        <v>103</v>
-      </c>
-      <c r="B26" s="41">
-        <v>1</v>
-      </c>
-      <c r="C26" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D26" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E26" s="78" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" s="78" t="s">
-        <v>6</v>
-      </c>
-      <c r="G26" s="43"/>
-      <c r="H26" s="43"/>
-      <c r="I26" s="43"/>
-      <c r="J26" s="43"/>
-      <c r="K26" s="43"/>
-      <c r="L26" s="43">
-        <v>0</v>
-      </c>
-      <c r="M26" s="43">
-        <v>0</v>
-      </c>
-      <c r="N26" s="43">
-        <v>0</v>
-      </c>
-      <c r="O26" s="43">
-        <v>0</v>
-      </c>
-      <c r="P26" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="43">
-        <v>10000</v>
-      </c>
-      <c r="R26" s="43">
-        <v>10000</v>
-      </c>
-      <c r="S26" s="43">
-        <v>10000</v>
-      </c>
-      <c r="T26" s="43">
-        <v>10000</v>
-      </c>
-      <c r="U26" s="43">
-        <v>10000</v>
-      </c>
-      <c r="V26" s="43">
-        <v>10000</v>
-      </c>
-      <c r="W26" s="43">
-        <v>10000</v>
-      </c>
-      <c r="X26" s="43">
-        <v>10000</v>
-      </c>
-      <c r="Y26" s="43">
-        <v>10000</v>
-      </c>
-      <c r="Z26" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AA26" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AB26" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AC26" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AD26" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AE26" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AF26" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AG26" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AH26" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AI26" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AJ26" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AK26" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AL26" s="43">
-        <f>AK26</f>
-      </c>
-      <c r="AM26" s="43">
-        <f>AL26</f>
-      </c>
-      <c r="AN26" s="43">
-        <f>AM26</f>
-      </c>
-      <c r="AO26" s="43">
-        <f>AN26</f>
-      </c>
-      <c r="AP26" s="43">
-        <f>AO26</f>
-      </c>
-      <c r="AQ26" s="43">
-        <f>AP26</f>
-      </c>
-      <c r="AR26" s="43">
-        <f>AQ26</f>
-      </c>
-      <c r="AS26" s="43">
-        <f>AR26</f>
-      </c>
-      <c r="AT26" s="43">
-        <f>AS26</f>
-      </c>
-      <c r="AU26" s="43">
-        <f>AT26</f>
-      </c>
-    </row>
-    <row r="27" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A27" s="47">
-        <f>A26</f>
-      </c>
-      <c r="B27" s="41">
-        <v>1</v>
-      </c>
-      <c r="C27" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E27" s="78" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" s="78" t="s">
-        <v>6</v>
-      </c>
-      <c r="G27" s="43"/>
-      <c r="H27" s="43"/>
-      <c r="I27" s="43"/>
-      <c r="J27" s="43"/>
-      <c r="K27" s="43"/>
-      <c r="L27" s="43">
-        <v>2000</v>
-      </c>
-      <c r="M27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="N27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="O27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="P27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="Q27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="R27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="S27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="T27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="U27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="V27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="W27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="X27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="Y27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="Z27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AA27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AB27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AC27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AD27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AE27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AF27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AG27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AH27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AI27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AJ27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AK27" s="43">
-        <v>10000</v>
-      </c>
-      <c r="AL27" s="43">
-        <f>AK27</f>
-      </c>
-      <c r="AM27" s="43">
-        <f>AL27</f>
-      </c>
-      <c r="AN27" s="43">
-        <f>AM27</f>
-      </c>
-      <c r="AO27" s="43">
-        <f>AN27</f>
-      </c>
-      <c r="AP27" s="43">
-        <f>AO27</f>
-      </c>
-      <c r="AQ27" s="43">
-        <f>AP27</f>
-      </c>
-      <c r="AR27" s="43">
-        <f>AQ27</f>
-      </c>
-      <c r="AS27" s="43">
-        <f>AR27</f>
-      </c>
-      <c r="AT27" s="43">
-        <f>AS27</f>
-      </c>
-      <c r="AU27" s="43">
-        <f>AT27</f>
-      </c>
-    </row>
-    <row r="28" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A28" s="47">
-        <f>A27</f>
-      </c>
-      <c r="B28" s="41">
-        <v>1</v>
-      </c>
-      <c r="C28" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D28" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E28" s="78" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" s="78" t="s">
-        <v>6</v>
-      </c>
-      <c r="G28" s="43"/>
-      <c r="H28" s="43"/>
-      <c r="I28" s="43"/>
-      <c r="J28" s="43"/>
-      <c r="K28" s="43"/>
-      <c r="L28" s="43">
-        <v>0</v>
-      </c>
-      <c r="M28" s="43">
-        <v>1000</v>
-      </c>
-      <c r="N28" s="43">
-        <f>M28</f>
-      </c>
-      <c r="O28" s="43">
-        <f>N28</f>
-      </c>
-      <c r="P28" s="43">
-        <f>O28</f>
-      </c>
-      <c r="Q28" s="43">
-        <f>P28</f>
-      </c>
-      <c r="R28" s="43">
-        <f>Q28</f>
-      </c>
-      <c r="S28" s="43">
-        <f>R28</f>
-      </c>
-      <c r="T28" s="43">
-        <f>S28</f>
-      </c>
-      <c r="U28" s="43">
-        <f>T28</f>
-      </c>
-      <c r="V28" s="43">
-        <f>U28</f>
-      </c>
-      <c r="W28" s="43">
-        <f>V28</f>
-      </c>
-      <c r="X28" s="43">
-        <f>W28</f>
-      </c>
-      <c r="Y28" s="43">
-        <f>X28</f>
-      </c>
-      <c r="Z28" s="43">
-        <f>Y28</f>
-      </c>
-      <c r="AA28" s="43">
-        <f>Z28</f>
-      </c>
-      <c r="AB28" s="43">
-        <f>AA28</f>
-      </c>
-      <c r="AC28" s="43">
-        <f>AB28</f>
-      </c>
-      <c r="AD28" s="43">
-        <f>AC28</f>
-      </c>
-      <c r="AE28" s="43">
-        <f>AD28</f>
-      </c>
-      <c r="AF28" s="43">
-        <f>AE28</f>
-      </c>
-      <c r="AG28" s="43">
-        <f>AF28</f>
-      </c>
-      <c r="AH28" s="43">
-        <f>AG28</f>
-      </c>
-      <c r="AI28" s="43">
-        <f>AH28</f>
-      </c>
-      <c r="AJ28" s="43">
-        <f>AI28</f>
-      </c>
-      <c r="AK28" s="43">
-        <f>AJ28</f>
-      </c>
-      <c r="AL28" s="43">
-        <f>AK28</f>
-      </c>
-      <c r="AM28" s="43">
-        <f>AL28</f>
-      </c>
-      <c r="AN28" s="43">
-        <f>AM28</f>
-      </c>
-      <c r="AO28" s="43">
-        <f>AN28</f>
-      </c>
-      <c r="AP28" s="43">
-        <f>AO28</f>
-      </c>
-      <c r="AQ28" s="43">
-        <f>AP28</f>
-      </c>
-      <c r="AR28" s="43">
-        <f>AQ28</f>
-      </c>
-      <c r="AS28" s="43">
-        <f>AR28</f>
-      </c>
-      <c r="AT28" s="43">
-        <f>AS28</f>
-      </c>
-      <c r="AU28" s="43">
-        <f>AT28</f>
-      </c>
-    </row>
-    <row r="29" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A29" s="47">
-        <f>A28</f>
-      </c>
-      <c r="B29" s="41">
-        <v>1</v>
-      </c>
-      <c r="C29" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D29" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E29" s="78" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="78" t="s">
-        <v>6</v>
-      </c>
-      <c r="G29" s="43"/>
-      <c r="H29" s="43"/>
-      <c r="I29" s="43"/>
-      <c r="J29" s="43"/>
-      <c r="K29" s="43"/>
-      <c r="L29" s="43">
-        <v>5</v>
-      </c>
-      <c r="M29" s="43">
-        <v>1000</v>
-      </c>
-      <c r="N29" s="43">
-        <v>1000</v>
-      </c>
-      <c r="O29" s="43">
-        <v>1000</v>
-      </c>
-      <c r="P29" s="43">
-        <v>1000</v>
-      </c>
-      <c r="Q29" s="43">
-        <f>P29</f>
-      </c>
-      <c r="R29" s="43">
-        <f>Q29+100</f>
-      </c>
-      <c r="S29" s="43">
-        <f>R29+100</f>
-      </c>
-      <c r="T29" s="43">
-        <f>S29+100</f>
-      </c>
-      <c r="U29" s="43">
-        <f>T29+100</f>
-      </c>
-      <c r="V29" s="43">
-        <f>U29+100</f>
-      </c>
-      <c r="W29" s="43">
-        <f>V29+100</f>
-      </c>
-      <c r="X29" s="43">
-        <f>W29+100</f>
-      </c>
-      <c r="Y29" s="43">
-        <f>X29+100</f>
-      </c>
-      <c r="Z29" s="43">
-        <f>Y29+100</f>
-      </c>
-      <c r="AA29" s="43">
-        <f>Z29+100</f>
-      </c>
-      <c r="AB29" s="43">
-        <f>AA29+100</f>
-      </c>
-      <c r="AC29" s="43">
-        <f>AB29+100</f>
-      </c>
-      <c r="AD29" s="43">
-        <f>AC29+100</f>
-      </c>
-      <c r="AE29" s="43">
-        <f>AD29+100</f>
-      </c>
-      <c r="AF29" s="43">
-        <f>AE29+100</f>
-      </c>
-      <c r="AG29" s="43">
-        <f>AF29+100</f>
-      </c>
-      <c r="AH29" s="43">
-        <f>AG29+100</f>
-      </c>
-      <c r="AI29" s="43">
-        <f>AH29+100</f>
-      </c>
-      <c r="AJ29" s="43">
-        <f>AI29+100</f>
-      </c>
-      <c r="AK29" s="43">
-        <f>AJ29+100</f>
-      </c>
-      <c r="AL29" s="43">
-        <f>AK29+100</f>
-      </c>
-      <c r="AM29" s="43">
-        <f>AL29+100</f>
-      </c>
-      <c r="AN29" s="43">
-        <f>AM29+100</f>
-      </c>
-      <c r="AO29" s="43">
-        <f>AN29+100</f>
-      </c>
-      <c r="AP29" s="43">
-        <f>AO29+100</f>
-      </c>
-      <c r="AQ29" s="43">
-        <f>AP29+100</f>
-      </c>
-      <c r="AR29" s="43">
-        <f>AQ29+100</f>
-      </c>
-      <c r="AS29" s="43">
-        <f>AR29+100</f>
-      </c>
-      <c r="AT29" s="43">
-        <f>AS29+100</f>
-      </c>
-      <c r="AU29" s="43">
-        <f>AT29+100</f>
-      </c>
-    </row>
-    <row r="30" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A30" s="47">
-        <f>A29</f>
-      </c>
-      <c r="B30" s="41">
-        <v>1</v>
-      </c>
-      <c r="C30" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E30" s="78" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" s="78" t="s">
-        <v>6</v>
-      </c>
-      <c r="G30" s="43"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="43"/>
-      <c r="J30" s="43"/>
-      <c r="K30" s="43"/>
-      <c r="L30" s="43">
-        <v>5</v>
-      </c>
-      <c r="M30" s="43">
-        <v>0</v>
-      </c>
-      <c r="N30" s="43">
-        <v>0</v>
-      </c>
-      <c r="O30" s="43">
-        <v>0</v>
-      </c>
-      <c r="P30" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="43">
-        <v>1000</v>
-      </c>
-      <c r="R30" s="43">
-        <f>Q30</f>
-      </c>
-      <c r="S30" s="43">
-        <f>R30</f>
-      </c>
-      <c r="T30" s="43">
-        <f>S30</f>
-      </c>
-      <c r="U30" s="43">
-        <f>T30</f>
-      </c>
-      <c r="V30" s="43">
-        <f>U30</f>
-      </c>
-      <c r="W30" s="43">
-        <f>V30</f>
-      </c>
-      <c r="X30" s="43">
-        <f>W30</f>
-      </c>
-      <c r="Y30" s="43">
-        <f>X30</f>
-      </c>
-      <c r="Z30" s="43">
-        <f>Y30</f>
-      </c>
-      <c r="AA30" s="43">
-        <f>Z30</f>
-      </c>
-      <c r="AB30" s="43">
-        <f>AA30</f>
-      </c>
-      <c r="AC30" s="43">
-        <f>AB30</f>
-      </c>
-      <c r="AD30" s="43">
-        <f>AC30</f>
-      </c>
-      <c r="AE30" s="43">
-        <f>AD30</f>
-      </c>
-      <c r="AF30" s="43">
-        <f>AE30</f>
-      </c>
-      <c r="AG30" s="43">
-        <f>AF30</f>
-      </c>
-      <c r="AH30" s="43">
-        <f>AG30</f>
-      </c>
-      <c r="AI30" s="43">
-        <f>AH30</f>
-      </c>
-      <c r="AJ30" s="43">
-        <f>AI30</f>
-      </c>
-      <c r="AK30" s="43">
-        <f>AJ30</f>
-      </c>
-      <c r="AL30" s="43">
-        <f>AK30</f>
-      </c>
-      <c r="AM30" s="43">
-        <f>AL30</f>
-      </c>
-      <c r="AN30" s="43">
-        <f>AM30</f>
-      </c>
-      <c r="AO30" s="43">
-        <f>AN30</f>
-      </c>
-      <c r="AP30" s="43">
-        <f>AO30</f>
-      </c>
-      <c r="AQ30" s="43">
-        <f>AP30</f>
-      </c>
-      <c r="AR30" s="43">
-        <f>AQ30</f>
-      </c>
-      <c r="AS30" s="43">
-        <f>AR30</f>
-      </c>
-      <c r="AT30" s="43">
-        <f>AS30</f>
-      </c>
-      <c r="AU30" s="43">
-        <f>AT30</f>
-      </c>
-    </row>
-    <row r="31" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A31" s="47">
-        <f>A30</f>
-      </c>
-      <c r="B31" s="41">
-        <v>1</v>
-      </c>
-      <c r="C31" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D31" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E31" s="78" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" s="78" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31" s="43"/>
-      <c r="H31" s="43"/>
-      <c r="I31" s="43"/>
-      <c r="J31" s="43"/>
-      <c r="K31" s="43"/>
-      <c r="L31" s="43">
-        <v>0</v>
-      </c>
-      <c r="M31" s="43">
-        <v>0</v>
-      </c>
-      <c r="N31" s="43">
-        <v>0</v>
-      </c>
-      <c r="O31" s="43">
-        <v>0</v>
-      </c>
-      <c r="P31" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="R31" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="S31" s="43">
-        <f>R31</f>
-      </c>
-      <c r="T31" s="43">
-        <f>S31</f>
-      </c>
-      <c r="U31" s="43">
-        <f>T31</f>
-      </c>
-      <c r="V31" s="43">
-        <f>U31</f>
-      </c>
-      <c r="W31" s="43">
-        <f>V31</f>
-      </c>
-      <c r="X31" s="43">
-        <f>W31</f>
-      </c>
-      <c r="Y31" s="43">
-        <f>X31</f>
-      </c>
-      <c r="Z31" s="43">
-        <f>Y31</f>
-      </c>
-      <c r="AA31" s="43">
-        <f>Z31</f>
-      </c>
-      <c r="AB31" s="43">
-        <f>AA31</f>
-      </c>
-      <c r="AC31" s="43">
-        <f>AB31</f>
-      </c>
-      <c r="AD31" s="43">
-        <f>AC31</f>
-      </c>
-      <c r="AE31" s="43">
-        <f>AD31</f>
-      </c>
-      <c r="AF31" s="43">
-        <f>AE31</f>
-      </c>
-      <c r="AG31" s="43">
-        <f>AF31</f>
-      </c>
-      <c r="AH31" s="43">
-        <f>AG31</f>
-      </c>
-      <c r="AI31" s="43">
-        <f>AH31</f>
-      </c>
-      <c r="AJ31" s="43">
-        <f>AI31</f>
-      </c>
-      <c r="AK31" s="43">
-        <f>AJ31</f>
-      </c>
-      <c r="AL31" s="43">
-        <f>AK31</f>
-      </c>
-      <c r="AM31" s="43">
-        <f>AL31</f>
-      </c>
-      <c r="AN31" s="43">
-        <f>AM31</f>
-      </c>
-      <c r="AO31" s="43">
-        <f>AN31</f>
-      </c>
-      <c r="AP31" s="43">
-        <f>AO31</f>
-      </c>
-      <c r="AQ31" s="43">
-        <f>AP31</f>
-      </c>
-      <c r="AR31" s="43">
-        <f>AQ31</f>
-      </c>
-      <c r="AS31" s="43">
-        <f>AR31</f>
-      </c>
-      <c r="AT31" s="43">
-        <f>AS31</f>
-      </c>
-      <c r="AU31" s="43">
-        <f>AT31</f>
-      </c>
-    </row>
-    <row r="32" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A32" s="47">
-        <f>A31</f>
-      </c>
-      <c r="B32" s="41">
-        <v>1</v>
-      </c>
-      <c r="C32" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D32" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E32" s="78" t="s">
-        <v>15</v>
-      </c>
-      <c r="F32" s="78" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32" s="43"/>
-      <c r="H32" s="43"/>
-      <c r="I32" s="43"/>
-      <c r="J32" s="43"/>
-      <c r="K32" s="43"/>
-      <c r="L32" s="43">
-        <v>0</v>
-      </c>
-      <c r="M32" s="43">
-        <v>0</v>
-      </c>
-      <c r="N32" s="43">
-        <v>0</v>
-      </c>
-      <c r="O32" s="43">
-        <v>0</v>
-      </c>
-      <c r="P32" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="R32" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="S32" s="43">
-        <f>R32</f>
-      </c>
-      <c r="T32" s="43">
-        <f>S32</f>
-      </c>
-      <c r="U32" s="43">
-        <f>T32</f>
-      </c>
-      <c r="V32" s="43">
-        <f>U32</f>
-      </c>
-      <c r="W32" s="43">
-        <f>V32</f>
-      </c>
-      <c r="X32" s="43">
-        <f>W32</f>
-      </c>
-      <c r="Y32" s="43">
-        <f>X32</f>
-      </c>
-      <c r="Z32" s="43">
-        <f>Y32</f>
-      </c>
-      <c r="AA32" s="43">
-        <f>Z32</f>
-      </c>
-      <c r="AB32" s="43">
-        <f>AA32</f>
-      </c>
-      <c r="AC32" s="43">
-        <f>AB32</f>
-      </c>
-      <c r="AD32" s="43">
-        <f>AC32</f>
-      </c>
-      <c r="AE32" s="43">
-        <f>AD32</f>
-      </c>
-      <c r="AF32" s="43">
-        <f>AE32</f>
-      </c>
-      <c r="AG32" s="43">
-        <f>AF32</f>
-      </c>
-      <c r="AH32" s="43">
-        <f>AG32</f>
-      </c>
-      <c r="AI32" s="43">
-        <f>AH32</f>
-      </c>
-      <c r="AJ32" s="43">
-        <f>AI32</f>
-      </c>
-      <c r="AK32" s="43">
-        <f>AJ32</f>
-      </c>
-      <c r="AL32" s="43">
-        <f>AK32</f>
-      </c>
-      <c r="AM32" s="43">
-        <f>AL32</f>
-      </c>
-      <c r="AN32" s="43">
-        <f>AM32</f>
-      </c>
-      <c r="AO32" s="43">
-        <f>AN32</f>
-      </c>
-      <c r="AP32" s="43">
-        <f>AO32</f>
-      </c>
-      <c r="AQ32" s="43">
-        <f>AP32</f>
-      </c>
-      <c r="AR32" s="43">
-        <f>AQ32</f>
-      </c>
-      <c r="AS32" s="43">
-        <f>AR32</f>
-      </c>
-      <c r="AT32" s="43">
-        <f>AS32</f>
-      </c>
-      <c r="AU32" s="43">
-        <f>AT32</f>
-      </c>
-    </row>
-    <row r="33" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A33" s="47">
-        <f>A32</f>
-      </c>
-      <c r="B33" s="41">
-        <v>1</v>
-      </c>
-      <c r="C33" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D33" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E33" s="78" t="s">
-        <v>16</v>
-      </c>
-      <c r="F33" s="78" t="s">
-        <v>14</v>
-      </c>
-      <c r="G33" s="43"/>
-      <c r="H33" s="43"/>
-      <c r="I33" s="43"/>
-      <c r="J33" s="43"/>
-      <c r="K33" s="43"/>
-      <c r="L33" s="43">
-        <v>0</v>
-      </c>
-      <c r="M33" s="43">
-        <v>0</v>
-      </c>
-      <c r="N33" s="43">
-        <v>0</v>
-      </c>
-      <c r="O33" s="43">
-        <v>0</v>
-      </c>
-      <c r="P33" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="R33" s="43">
-        <v>0</v>
-      </c>
-      <c r="S33" s="43">
-        <v>0</v>
-      </c>
-      <c r="T33" s="43">
-        <v>0</v>
-      </c>
-      <c r="U33" s="43">
-        <f>T33</f>
-      </c>
-      <c r="V33" s="43">
-        <f>U33</f>
-      </c>
-      <c r="W33" s="43">
-        <v>0</v>
-      </c>
-      <c r="X33" s="43">
-        <f>W33</f>
-      </c>
-      <c r="Y33" s="43">
-        <f>X33</f>
-      </c>
-      <c r="Z33" s="43">
-        <f>Y33</f>
-      </c>
-      <c r="AA33" s="43">
-        <v>0</v>
-      </c>
-      <c r="AB33" s="43">
-        <f>AA33</f>
-      </c>
-      <c r="AC33" s="43">
-        <f>AB33</f>
-      </c>
-      <c r="AD33" s="43">
-        <f>AC33</f>
-      </c>
-      <c r="AE33" s="43">
-        <f>AD33</f>
-      </c>
-      <c r="AF33" s="43">
-        <f>AE33</f>
-      </c>
-      <c r="AG33" s="43">
-        <f>AF33</f>
-      </c>
-      <c r="AH33" s="43">
-        <f>AG33</f>
-      </c>
-      <c r="AI33" s="43">
-        <f>AH33</f>
-      </c>
-      <c r="AJ33" s="43">
-        <f>AI33</f>
-      </c>
-      <c r="AK33" s="43">
-        <f>AJ33</f>
-      </c>
-      <c r="AL33" s="43">
-        <f>AK33</f>
-      </c>
-      <c r="AM33" s="43">
-        <f>AL33</f>
-      </c>
-      <c r="AN33" s="43">
-        <f>AM33</f>
-      </c>
-      <c r="AO33" s="43">
-        <f>AN33</f>
-      </c>
-      <c r="AP33" s="43">
-        <f>AO33</f>
-      </c>
-      <c r="AQ33" s="43">
-        <f>AP33</f>
-      </c>
-      <c r="AR33" s="43">
-        <f>AQ33</f>
-      </c>
-      <c r="AS33" s="43">
-        <f>AR33</f>
-      </c>
-      <c r="AT33" s="43">
-        <f>AS33</f>
-      </c>
-      <c r="AU33" s="43">
-        <f>AT33</f>
-      </c>
-    </row>
-    <row r="34" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A34" s="47">
-        <f>A33</f>
-      </c>
-      <c r="B34" s="41">
-        <v>1</v>
-      </c>
-      <c r="C34" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D34" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E34" s="78" t="s">
-        <v>17</v>
-      </c>
-      <c r="F34" s="78" t="s">
-        <v>14</v>
-      </c>
-      <c r="G34" s="43"/>
-      <c r="H34" s="43"/>
-      <c r="I34" s="43"/>
-      <c r="J34" s="43"/>
-      <c r="K34" s="43"/>
-      <c r="L34" s="43">
-        <v>0</v>
-      </c>
-      <c r="M34" s="43">
-        <v>0</v>
-      </c>
-      <c r="N34" s="43">
-        <v>0</v>
-      </c>
-      <c r="O34" s="43">
-        <v>0</v>
-      </c>
-      <c r="P34" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="R34" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="S34" s="43">
-        <f>R34</f>
-      </c>
-      <c r="T34" s="43">
-        <f>S34</f>
-      </c>
-      <c r="U34" s="43">
-        <f>T34</f>
-      </c>
-      <c r="V34" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="W34" s="43">
-        <v>0</v>
-      </c>
-      <c r="X34" s="43">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="43">
-        <f>X34</f>
-      </c>
-      <c r="Z34" s="43">
-        <f>Y34</f>
-      </c>
-      <c r="AA34" s="43">
-        <f>Z34</f>
-      </c>
-      <c r="AB34" s="43">
-        <v>0</v>
-      </c>
-      <c r="AC34" s="43">
-        <f>AB34</f>
-      </c>
-      <c r="AD34" s="43">
-        <f>AC34</f>
-      </c>
-      <c r="AE34" s="43">
-        <f>AD34</f>
-      </c>
-      <c r="AF34" s="43">
-        <v>0</v>
-      </c>
-      <c r="AG34" s="43">
-        <f>AF34</f>
-      </c>
-      <c r="AH34" s="43">
-        <f>AG34</f>
-      </c>
-      <c r="AI34" s="43">
-        <f>AH34</f>
-      </c>
-      <c r="AJ34" s="43">
-        <f>AI34</f>
-      </c>
-      <c r="AK34" s="43">
-        <f>AJ34</f>
-      </c>
-      <c r="AL34" s="43">
-        <f>AK34</f>
-      </c>
-      <c r="AM34" s="43">
-        <f>AL34</f>
-      </c>
-      <c r="AN34" s="43">
-        <f>AM34</f>
-      </c>
-      <c r="AO34" s="43">
-        <f>AN34</f>
-      </c>
-      <c r="AP34" s="43">
-        <f>AO34</f>
-      </c>
-      <c r="AQ34" s="43">
-        <f>AP34</f>
-      </c>
-      <c r="AR34" s="43">
-        <f>AQ34</f>
-      </c>
-      <c r="AS34" s="43">
-        <f>AR34</f>
-      </c>
-      <c r="AT34" s="43">
-        <f>AS34</f>
-      </c>
-      <c r="AU34" s="43">
-        <f>AT34</f>
-      </c>
-    </row>
-    <row r="35" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A35" s="47">
-        <f>A34</f>
-      </c>
-      <c r="B35" s="41">
-        <v>1</v>
-      </c>
-      <c r="C35" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D35" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E35" s="78" t="s">
-        <v>18</v>
-      </c>
-      <c r="F35" s="78" t="s">
-        <v>14</v>
-      </c>
-      <c r="G35" s="43"/>
-      <c r="H35" s="43"/>
-      <c r="I35" s="43"/>
-      <c r="J35" s="43"/>
-      <c r="K35" s="43"/>
-      <c r="L35" s="43">
-        <v>0</v>
-      </c>
-      <c r="M35" s="43">
-        <v>0</v>
-      </c>
-      <c r="N35" s="43">
-        <v>0</v>
-      </c>
-      <c r="O35" s="43">
-        <v>0</v>
-      </c>
-      <c r="P35" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="R35" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="S35" s="43">
-        <f>R35</f>
-      </c>
-      <c r="T35" s="43">
-        <f>S35</f>
-      </c>
-      <c r="U35" s="43">
-        <f>T35</f>
-      </c>
-      <c r="V35" s="43">
-        <f>U35</f>
-      </c>
-      <c r="W35" s="43">
-        <f>V35</f>
-      </c>
-      <c r="X35" s="43">
-        <f>W35</f>
-      </c>
-      <c r="Y35" s="43">
-        <f>X35</f>
-      </c>
-      <c r="Z35" s="43">
-        <f>Y35</f>
-      </c>
-      <c r="AA35" s="43">
-        <f>Z35</f>
-      </c>
-      <c r="AB35" s="43">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="43">
-        <v>0</v>
-      </c>
-      <c r="AD35" s="43">
-        <v>0</v>
-      </c>
-      <c r="AE35" s="43">
-        <f>AD35</f>
-      </c>
-      <c r="AF35" s="43">
-        <f>AE35</f>
-      </c>
-      <c r="AG35" s="43">
-        <v>0</v>
-      </c>
-      <c r="AH35" s="43">
-        <f>AG35</f>
-      </c>
-      <c r="AI35" s="43">
-        <f>AH35</f>
-      </c>
-      <c r="AJ35" s="43">
-        <f>AI35</f>
-      </c>
-      <c r="AK35" s="43">
-        <v>0</v>
-      </c>
-      <c r="AL35" s="43">
-        <f>AK35</f>
-      </c>
-      <c r="AM35" s="43">
-        <f>AL35</f>
-      </c>
-      <c r="AN35" s="43">
-        <f>AM35</f>
-      </c>
-      <c r="AO35" s="43">
-        <f>AN35</f>
-      </c>
-      <c r="AP35" s="43">
-        <f>AO35</f>
-      </c>
-      <c r="AQ35" s="43">
-        <f>AP35</f>
-      </c>
-      <c r="AR35" s="43">
-        <f>AQ35</f>
-      </c>
-      <c r="AS35" s="43">
-        <f>AR35</f>
-      </c>
-      <c r="AT35" s="43">
-        <f>AS35</f>
-      </c>
-      <c r="AU35" s="43">
-        <f>AT35</f>
-      </c>
-    </row>
-    <row r="36" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A36" s="47">
-        <f>A35</f>
-      </c>
-      <c r="B36" s="41">
-        <v>1</v>
-      </c>
-      <c r="C36" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D36" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E36" s="78" t="s">
-        <v>19</v>
-      </c>
-      <c r="F36" s="78" t="s">
-        <v>14</v>
-      </c>
-      <c r="G36" s="43"/>
-      <c r="H36" s="43"/>
-      <c r="I36" s="43"/>
-      <c r="J36" s="43"/>
-      <c r="K36" s="43"/>
-      <c r="L36" s="43">
-        <v>0</v>
-      </c>
-      <c r="M36" s="43">
-        <v>0</v>
-      </c>
-      <c r="N36" s="43">
-        <v>0</v>
-      </c>
-      <c r="O36" s="43">
-        <v>0</v>
-      </c>
-      <c r="P36" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="R36" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="S36" s="43">
-        <f>R36</f>
-      </c>
-      <c r="T36" s="43">
-        <f>S36</f>
-      </c>
-      <c r="U36" s="43">
-        <f>T36</f>
-      </c>
-      <c r="V36" s="43">
-        <f>U36</f>
-      </c>
-      <c r="W36" s="43">
-        <f>V36</f>
-      </c>
-      <c r="X36" s="43">
-        <f>W36</f>
-      </c>
-      <c r="Y36" s="43">
-        <f>X36</f>
-      </c>
-      <c r="Z36" s="43">
-        <f>Y36</f>
-      </c>
-      <c r="AA36" s="43">
-        <f>Z36</f>
-      </c>
-      <c r="AB36" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="AC36" s="43">
-        <f>AB36</f>
-      </c>
-      <c r="AD36" s="43">
-        <f>AC36</f>
-      </c>
-      <c r="AE36" s="43">
-        <f>AD36</f>
-      </c>
-      <c r="AF36" s="43">
-        <f>AE36</f>
-      </c>
-      <c r="AG36" s="43">
-        <v>0</v>
-      </c>
-      <c r="AH36" s="43">
-        <f>AG36</f>
-      </c>
-      <c r="AI36" s="43">
-        <f>AH36</f>
-      </c>
-      <c r="AJ36" s="43">
-        <f>AI36</f>
-      </c>
-      <c r="AK36" s="43">
-        <f>AJ36</f>
-      </c>
-      <c r="AL36" s="43">
-        <v>0</v>
-      </c>
-      <c r="AM36" s="43">
-        <f>AL36</f>
-      </c>
-      <c r="AN36" s="43">
-        <f>AM36</f>
-      </c>
-      <c r="AO36" s="43">
-        <f>AN36</f>
-      </c>
-      <c r="AP36" s="43">
-        <f>AO36</f>
-      </c>
-      <c r="AQ36" s="43">
-        <f>AP36</f>
-      </c>
-      <c r="AR36" s="43">
-        <f>AQ36</f>
-      </c>
-      <c r="AS36" s="43">
-        <f>AR36</f>
-      </c>
-      <c r="AT36" s="43">
-        <f>AS36</f>
-      </c>
-      <c r="AU36" s="43">
-        <f>AT36</f>
-      </c>
-    </row>
-    <row r="37" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A37" s="47">
-        <f>A36</f>
-      </c>
-      <c r="B37" s="41">
-        <v>1</v>
-      </c>
-      <c r="C37" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D37" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E37" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="F37" s="78" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37" s="43"/>
-      <c r="H37" s="43"/>
-      <c r="I37" s="43"/>
-      <c r="J37" s="43"/>
-      <c r="K37" s="43"/>
-      <c r="L37" s="43">
-        <v>0</v>
-      </c>
-      <c r="M37" s="43">
-        <v>0</v>
-      </c>
-      <c r="N37" s="43">
-        <v>0</v>
-      </c>
-      <c r="O37" s="43">
-        <v>0</v>
-      </c>
-      <c r="P37" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="R37" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="S37" s="43">
-        <f>R37</f>
-      </c>
-      <c r="T37" s="43">
-        <f>S37</f>
-      </c>
-      <c r="U37" s="43">
-        <f>T37</f>
-      </c>
-      <c r="V37" s="43">
-        <f>U37</f>
-      </c>
-      <c r="W37" s="43">
-        <f>V37</f>
-      </c>
-      <c r="X37" s="43">
-        <f>W37</f>
-      </c>
-      <c r="Y37" s="43">
-        <f>X37</f>
-      </c>
-      <c r="Z37" s="43">
-        <f>Y37</f>
-      </c>
-      <c r="AA37" s="43">
-        <f>Z37</f>
-      </c>
-      <c r="AB37" s="43">
-        <f>AA37</f>
-      </c>
-      <c r="AC37" s="43">
-        <f>AB37</f>
-      </c>
-      <c r="AD37" s="43">
-        <f>AC37</f>
-      </c>
-      <c r="AE37" s="43">
-        <f>AD37</f>
-      </c>
-      <c r="AF37" s="43">
-        <f>AE37</f>
-      </c>
-      <c r="AG37" s="43">
-        <f>AF37</f>
-      </c>
-      <c r="AH37" s="43">
-        <f>AG37</f>
-      </c>
-      <c r="AI37" s="43">
-        <f>AH37</f>
-      </c>
-      <c r="AJ37" s="43">
-        <f>AI37</f>
-      </c>
-      <c r="AK37" s="43">
-        <f>AJ37</f>
-      </c>
-      <c r="AL37" s="43">
-        <v>0</v>
-      </c>
-      <c r="AM37" s="43">
-        <f>AL37</f>
-      </c>
-      <c r="AN37" s="43">
-        <f>AM37</f>
-      </c>
-      <c r="AO37" s="43">
-        <f>AN37</f>
-      </c>
-      <c r="AP37" s="43">
-        <f>AO37</f>
-      </c>
-      <c r="AQ37" s="43">
-        <v>0</v>
-      </c>
-      <c r="AR37" s="43">
-        <f>AQ37</f>
-      </c>
-      <c r="AS37" s="43">
-        <f>AR37</f>
-      </c>
-      <c r="AT37" s="43">
-        <f>AS37</f>
-      </c>
-      <c r="AU37" s="43">
-        <f>AT37</f>
-      </c>
-    </row>
-    <row r="38" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A38" s="47">
-        <f>A33</f>
-      </c>
-      <c r="B38" s="41">
-        <v>1</v>
-      </c>
-      <c r="C38" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D38" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E38" s="78" t="s">
-        <v>21</v>
-      </c>
-      <c r="F38" s="78" t="s">
-        <v>14</v>
-      </c>
-      <c r="G38" s="43"/>
-      <c r="H38" s="43"/>
-      <c r="I38" s="43"/>
-      <c r="J38" s="43"/>
-      <c r="K38" s="43"/>
-      <c r="L38" s="43">
-        <v>0</v>
-      </c>
-      <c r="M38" s="43">
-        <v>0</v>
-      </c>
-      <c r="N38" s="43">
-        <v>0</v>
-      </c>
-      <c r="O38" s="43">
-        <v>0</v>
-      </c>
-      <c r="P38" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="R38" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="S38" s="43">
-        <f>R38</f>
-      </c>
-      <c r="T38" s="43">
-        <f>S38</f>
-      </c>
-      <c r="U38" s="43">
-        <f>T38</f>
-      </c>
-      <c r="V38" s="43">
-        <f>U38</f>
-      </c>
-      <c r="W38" s="43">
-        <f>V38</f>
-      </c>
-      <c r="X38" s="43">
-        <f>W38</f>
-      </c>
-      <c r="Y38" s="43">
-        <f>X38</f>
-      </c>
-      <c r="Z38" s="43">
-        <f>Y38</f>
-      </c>
-      <c r="AA38" s="43">
-        <f>Z38</f>
-      </c>
-      <c r="AB38" s="43">
-        <f>AA38</f>
-      </c>
-      <c r="AC38" s="43">
-        <f>AB38</f>
-      </c>
-      <c r="AD38" s="43">
-        <f>AC38</f>
-      </c>
-      <c r="AE38" s="43">
-        <f>AD38</f>
-      </c>
-      <c r="AF38" s="43">
-        <f>AE38</f>
-      </c>
-      <c r="AG38" s="43">
-        <f>AF38</f>
-      </c>
-      <c r="AH38" s="43">
-        <f>AG38</f>
-      </c>
-      <c r="AI38" s="43">
-        <f>AH38</f>
-      </c>
-      <c r="AJ38" s="43">
-        <f>AI38</f>
-      </c>
-      <c r="AK38" s="43">
-        <f>AJ38</f>
-      </c>
-      <c r="AL38" s="43">
-        <f>AK38</f>
-      </c>
-      <c r="AM38" s="43">
-        <f>AL38</f>
-      </c>
-      <c r="AN38" s="43">
-        <f>AM38</f>
-      </c>
-      <c r="AO38" s="43">
-        <f>AN38</f>
-      </c>
-      <c r="AP38" s="43">
-        <f>AO38</f>
-      </c>
-      <c r="AQ38" s="43">
-        <f>AP38</f>
-      </c>
-      <c r="AR38" s="43">
-        <f>AQ38</f>
-      </c>
-      <c r="AS38" s="43">
-        <f>AR38</f>
-      </c>
-      <c r="AT38" s="43">
-        <f>AS38</f>
-      </c>
-      <c r="AU38" s="43">
-        <f>AT38</f>
-      </c>
-    </row>
-    <row r="39" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A39" s="48">
-        <f>A32</f>
-      </c>
-      <c r="B39" s="49">
-        <v>1</v>
-      </c>
-      <c r="C39" s="49" t="s">
-        <v>94</v>
-      </c>
-      <c r="D39" s="49" t="s">
-        <v>4</v>
-      </c>
-      <c r="E39" s="80" t="s">
-        <v>24</v>
-      </c>
-      <c r="F39" s="80" t="s">
-        <v>14</v>
-      </c>
-      <c r="G39" s="51"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="51"/>
-      <c r="J39" s="51"/>
-      <c r="K39" s="51"/>
-      <c r="L39" s="51">
-        <v>0</v>
-      </c>
-      <c r="M39" s="51">
-        <v>0</v>
-      </c>
-      <c r="N39" s="51">
-        <v>0</v>
-      </c>
-      <c r="O39" s="51">
-        <v>0</v>
-      </c>
-      <c r="P39" s="51">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="51">
-        <v>0</v>
-      </c>
-      <c r="R39" s="51">
-        <v>0</v>
-      </c>
-      <c r="S39" s="51">
-        <v>0</v>
-      </c>
-      <c r="T39" s="51">
-        <v>0</v>
-      </c>
-      <c r="U39" s="51">
-        <v>0</v>
-      </c>
-      <c r="V39" s="51">
-        <v>0</v>
-      </c>
-      <c r="W39" s="51">
-        <v>0</v>
-      </c>
-      <c r="X39" s="51">
-        <v>0</v>
-      </c>
-      <c r="Y39" s="51">
-        <v>0</v>
-      </c>
-      <c r="Z39" s="51">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="51">
-        <v>0</v>
-      </c>
-      <c r="AB39" s="51">
-        <v>0</v>
-      </c>
-      <c r="AC39" s="51">
-        <v>0</v>
-      </c>
-      <c r="AD39" s="51">
-        <v>0</v>
-      </c>
-      <c r="AE39" s="51">
-        <v>0</v>
-      </c>
-      <c r="AF39" s="51">
-        <v>0</v>
-      </c>
-      <c r="AG39" s="51">
-        <v>0</v>
-      </c>
-      <c r="AH39" s="51">
-        <v>0</v>
-      </c>
-      <c r="AI39" s="51">
-        <v>0</v>
-      </c>
-      <c r="AJ39" s="51">
-        <v>0</v>
-      </c>
-      <c r="AK39" s="51">
-        <v>0</v>
-      </c>
-      <c r="AL39" s="51">
-        <v>0</v>
-      </c>
-      <c r="AM39" s="51">
-        <v>0</v>
-      </c>
-      <c r="AN39" s="51">
-        <v>0</v>
-      </c>
-      <c r="AO39" s="51">
-        <v>0</v>
-      </c>
-      <c r="AP39" s="51">
-        <v>0</v>
-      </c>
-      <c r="AQ39" s="51">
-        <v>0</v>
-      </c>
-      <c r="AR39" s="51">
-        <v>0</v>
-      </c>
-      <c r="AS39" s="51">
-        <v>0</v>
-      </c>
-      <c r="AT39" s="51">
-        <v>0</v>
-      </c>
-      <c r="AU39" s="51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A40" s="47">
-        <f>A35</f>
-      </c>
-      <c r="B40" s="41">
-        <v>1</v>
-      </c>
-      <c r="C40" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D40" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E40" s="78" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" s="78" t="s">
-        <v>14</v>
-      </c>
-      <c r="G40" s="43"/>
-      <c r="H40" s="43"/>
-      <c r="I40" s="43"/>
-      <c r="J40" s="43"/>
-      <c r="K40" s="43"/>
-      <c r="L40" s="43">
-        <v>0</v>
-      </c>
-      <c r="M40" s="43">
-        <f>L40</f>
-      </c>
-      <c r="N40" s="43">
-        <f>M40</f>
-      </c>
-      <c r="O40" s="43">
-        <f>N40</f>
-      </c>
-      <c r="P40" s="43">
-        <f>O40</f>
-      </c>
-      <c r="Q40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="R40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="S40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="T40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="U40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="V40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="W40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="X40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="Y40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="Z40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="AA40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="AB40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="AC40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="AD40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="AE40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="AF40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="AG40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="AH40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="AI40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="AJ40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="AK40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="AL40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="AM40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="AN40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="AO40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="AP40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="AQ40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="AR40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="AS40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="AT40" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="AU40" s="43" t="s">
-        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/scenarios/Coal_Flexibilisation/sub_scenarios/extendable_technologies.xlsx
+++ b/scenarios/Coal_Flexibilisation/sub_scenarios/extendable_technologies.xlsx
@@ -65536,10 +65536,10 @@
         <v>0</v>
       </c>
       <c r="P3" s="71">
-        <f>O2</f>
+        <v>0</v>
       </c>
       <c r="Q3" s="71">
-        <f>P2</f>
+        <v>0</v>
       </c>
       <c r="R3" s="71">
         <v>0</v>
@@ -65569,37 +65569,37 @@
         <v>0</v>
       </c>
       <c r="AA3" s="71">
-        <f>Z2</f>
+        <v>0</v>
       </c>
       <c r="AB3" s="71">
-        <f>AA2</f>
+        <v>0</v>
       </c>
       <c r="AC3" s="71">
-        <f>AB2</f>
+        <v>0</v>
       </c>
       <c r="AD3" s="71">
-        <f>AC2</f>
+        <v>0</v>
       </c>
       <c r="AE3" s="71">
-        <f>AD2</f>
+        <v>0</v>
       </c>
       <c r="AF3" s="71">
-        <f>AE2</f>
+        <v>0</v>
       </c>
       <c r="AG3" s="71">
-        <f>AF2</f>
+        <v>0</v>
       </c>
       <c r="AH3" s="71">
-        <f>AG2</f>
+        <v>0</v>
       </c>
       <c r="AI3" s="71">
-        <f>AH2</f>
+        <v>0</v>
       </c>
       <c r="AJ3" s="71">
-        <f>AI2</f>
+        <v>0</v>
       </c>
       <c r="AK3" s="71">
-        <f>AJ2</f>
+        <v>0</v>
       </c>
       <c r="AL3" s="71">
         <f>AK2</f>
@@ -65682,7 +65682,7 @@
         <v>0</v>
       </c>
       <c r="Q4" s="43">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="R4" s="71">
         <v>0</v>
@@ -65712,37 +65712,37 @@
         <v>0</v>
       </c>
       <c r="AA4" s="71">
-        <f>Z3</f>
+        <v>0</v>
       </c>
       <c r="AB4" s="71">
-        <f>AA3</f>
+        <v>0</v>
       </c>
       <c r="AC4" s="71">
-        <f>AB3</f>
+        <v>0</v>
       </c>
       <c r="AD4" s="71">
-        <f>AC3</f>
+        <v>0</v>
       </c>
       <c r="AE4" s="71">
-        <f>AD3</f>
+        <v>0</v>
       </c>
       <c r="AF4" s="71">
-        <f>AE3</f>
+        <v>0</v>
       </c>
       <c r="AG4" s="71">
-        <f>AF3</f>
+        <v>0</v>
       </c>
       <c r="AH4" s="71">
-        <f>AG3</f>
+        <v>0</v>
       </c>
       <c r="AI4" s="71">
-        <f>AH3</f>
+        <v>0</v>
       </c>
       <c r="AJ4" s="71">
-        <f>AI3</f>
+        <v>0</v>
       </c>
       <c r="AK4" s="71">
-        <f>AJ3</f>
+        <v>0</v>
       </c>
       <c r="AL4" s="71">
         <f>AK3</f>
@@ -65825,7 +65825,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="51">
-        <v>2100</v>
+        <v>2102</v>
       </c>
       <c r="R5" s="71">
         <v>0</v>
@@ -65855,37 +65855,37 @@
         <v>0</v>
       </c>
       <c r="AA5" s="71">
-        <f>Z4</f>
+        <v>0</v>
       </c>
       <c r="AB5" s="71">
-        <f>AA4</f>
+        <v>0</v>
       </c>
       <c r="AC5" s="71">
-        <f>AB4</f>
+        <v>0</v>
       </c>
       <c r="AD5" s="71">
-        <f>AC4</f>
+        <v>0</v>
       </c>
       <c r="AE5" s="71">
-        <f>AD4</f>
+        <v>0</v>
       </c>
       <c r="AF5" s="71">
-        <f>AE4</f>
+        <v>0</v>
       </c>
       <c r="AG5" s="71">
-        <f>AF4</f>
+        <v>0</v>
       </c>
       <c r="AH5" s="71">
-        <f>AG4</f>
+        <v>0</v>
       </c>
       <c r="AI5" s="71">
-        <f>AH4</f>
+        <v>0</v>
       </c>
       <c r="AJ5" s="71">
-        <f>AI4</f>
+        <v>0</v>
       </c>
       <c r="AK5" s="71">
-        <f>AJ4</f>
+        <v>0</v>
       </c>
       <c r="AL5" s="71">
         <f>AK4</f>
@@ -65968,7 +65968,7 @@
         <v>0</v>
       </c>
       <c r="Q6" s="43">
-        <v>900</v>
+        <v>1795</v>
       </c>
       <c r="R6" s="71">
         <v>0</v>
@@ -65998,37 +65998,37 @@
         <v>0</v>
       </c>
       <c r="AA6" s="71">
-        <f>Z5</f>
+        <v>0</v>
       </c>
       <c r="AB6" s="71">
-        <f>AA5</f>
+        <v>0</v>
       </c>
       <c r="AC6" s="71">
-        <f>AB5</f>
+        <v>0</v>
       </c>
       <c r="AD6" s="71">
-        <f>AC5</f>
+        <v>0</v>
       </c>
       <c r="AE6" s="71">
-        <f>AD5</f>
+        <v>0</v>
       </c>
       <c r="AF6" s="71">
-        <f>AE5</f>
+        <v>0</v>
       </c>
       <c r="AG6" s="71">
-        <f>AF5</f>
+        <v>0</v>
       </c>
       <c r="AH6" s="71">
-        <f>AG5</f>
+        <v>0</v>
       </c>
       <c r="AI6" s="71">
-        <f>AH5</f>
+        <v>0</v>
       </c>
       <c r="AJ6" s="71">
-        <f>AI5</f>
+        <v>0</v>
       </c>
       <c r="AK6" s="71">
-        <f>AJ5</f>
+        <v>0</v>
       </c>
       <c r="AL6" s="71">
         <f>AK5</f>
@@ -66111,7 +66111,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="51">
-        <v>2100</v>
+        <v>4205</v>
       </c>
       <c r="R7" s="71">
         <v>0</v>
@@ -66141,37 +66141,37 @@
         <v>0</v>
       </c>
       <c r="AA7" s="71">
-        <f>Z6</f>
+        <v>0</v>
       </c>
       <c r="AB7" s="71">
-        <f>AA6</f>
+        <v>0</v>
       </c>
       <c r="AC7" s="71">
-        <f>AB6</f>
+        <v>0</v>
       </c>
       <c r="AD7" s="71">
-        <f>AC6</f>
+        <v>0</v>
       </c>
       <c r="AE7" s="71">
-        <f>AD6</f>
+        <v>0</v>
       </c>
       <c r="AF7" s="71">
-        <f>AE6</f>
+        <v>0</v>
       </c>
       <c r="AG7" s="71">
-        <f>AF6</f>
+        <v>0</v>
       </c>
       <c r="AH7" s="71">
-        <f>AG6</f>
+        <v>0</v>
       </c>
       <c r="AI7" s="71">
-        <f>AH6</f>
+        <v>0</v>
       </c>
       <c r="AJ7" s="71">
-        <f>AI6</f>
+        <v>0</v>
       </c>
       <c r="AK7" s="71">
-        <f>AJ6</f>
+        <v>0</v>
       </c>
       <c r="AL7" s="71">
         <f>AK6</f>
@@ -66284,37 +66284,37 @@
         <v>0</v>
       </c>
       <c r="AA8" s="71">
-        <f>Z7</f>
+        <v>0</v>
       </c>
       <c r="AB8" s="71">
-        <f>AA7</f>
+        <v>0</v>
       </c>
       <c r="AC8" s="71">
-        <f>AB7</f>
+        <v>0</v>
       </c>
       <c r="AD8" s="71">
-        <f>AC7</f>
+        <v>0</v>
       </c>
       <c r="AE8" s="71">
-        <f>AD7</f>
+        <v>0</v>
       </c>
       <c r="AF8" s="71">
-        <f>AE7</f>
+        <v>0</v>
       </c>
       <c r="AG8" s="71">
-        <f>AF7</f>
+        <v>0</v>
       </c>
       <c r="AH8" s="71">
-        <f>AG7</f>
+        <v>0</v>
       </c>
       <c r="AI8" s="71">
-        <f>AH7</f>
+        <v>0</v>
       </c>
       <c r="AJ8" s="71">
-        <f>AI7</f>
+        <v>0</v>
       </c>
       <c r="AK8" s="71">
-        <f>AJ7</f>
+        <v>0</v>
       </c>
       <c r="AL8" s="71">
         <f>AK7</f>
@@ -66427,37 +66427,37 @@
         <v>0</v>
       </c>
       <c r="AA9" s="71">
-        <f>Z8</f>
+        <v>0</v>
       </c>
       <c r="AB9" s="71">
-        <f>AA8</f>
+        <v>0</v>
       </c>
       <c r="AC9" s="71">
-        <f>AB8</f>
+        <v>0</v>
       </c>
       <c r="AD9" s="71">
-        <f>AC8</f>
+        <v>0</v>
       </c>
       <c r="AE9" s="71">
-        <f>AD8</f>
+        <v>0</v>
       </c>
       <c r="AF9" s="71">
-        <f>AE8</f>
+        <v>0</v>
       </c>
       <c r="AG9" s="71">
-        <f>AF8</f>
+        <v>0</v>
       </c>
       <c r="AH9" s="71">
-        <f>AG8</f>
+        <v>0</v>
       </c>
       <c r="AI9" s="71">
-        <f>AH8</f>
+        <v>0</v>
       </c>
       <c r="AJ9" s="71">
-        <f>AI8</f>
+        <v>0</v>
       </c>
       <c r="AK9" s="71">
-        <f>AJ8</f>
+        <v>0</v>
       </c>
       <c r="AL9" s="71">
         <f>AK8</f>
@@ -66491,43 +66491,119 @@
       </c>
     </row>
     <row r="10" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A10" s="56"/>
-      <c r="B10" s="56"/>
-      <c r="C10" s="56"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="56"/>
-      <c r="K10" s="56"/>
-      <c r="L10" s="56"/>
-      <c r="M10" s="56"/>
-      <c r="N10" s="56"/>
-      <c r="O10" s="56"/>
-      <c r="P10" s="56"/>
-      <c r="Q10" s="56"/>
-      <c r="R10" s="56"/>
-      <c r="S10" s="56"/>
-      <c r="T10" s="56"/>
-      <c r="U10" s="56"/>
-      <c r="V10" s="56"/>
-      <c r="W10" s="56"/>
-      <c r="X10" s="56"/>
-      <c r="Y10" s="56"/>
-      <c r="Z10" s="56"/>
-      <c r="AA10" s="56"/>
-      <c r="AB10" s="56"/>
-      <c r="AC10" s="56"/>
-      <c r="AD10" s="56"/>
-      <c r="AE10" s="56"/>
-      <c r="AF10" s="56"/>
-      <c r="AG10" s="56"/>
-      <c r="AH10" s="56"/>
-      <c r="AI10" s="56"/>
-      <c r="AJ10" s="56"/>
-      <c r="AK10" s="56"/>
+      <c r="A10" s="61" t="inlineStr">
+        <is>
+          <t>IRP25_GAS</t>
+        </is>
+      </c>
+      <c r="B10" s="68">
+        <v>1</v>
+      </c>
+      <c r="C10" s="69" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="70" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="70" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="71">
+        <v>0</v>
+      </c>
+      <c r="H10" s="71">
+        <v>0</v>
+      </c>
+      <c r="I10" s="71">
+        <v>0</v>
+      </c>
+      <c r="J10" s="71">
+        <v>0</v>
+      </c>
+      <c r="K10" s="71">
+        <v>0</v>
+      </c>
+      <c r="L10" s="71">
+        <v>0</v>
+      </c>
+      <c r="M10" s="71">
+        <v>0</v>
+      </c>
+      <c r="N10" s="71">
+        <v>0</v>
+      </c>
+      <c r="O10" s="71">
+        <v>0</v>
+      </c>
+      <c r="P10" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="71">
+        <v>1795</v>
+      </c>
+      <c r="R10" s="71">
+        <v>0</v>
+      </c>
+      <c r="S10" s="71">
+        <v>0</v>
+      </c>
+      <c r="T10" s="71">
+        <v>0</v>
+      </c>
+      <c r="U10" s="71">
+        <v>0</v>
+      </c>
+      <c r="V10" s="71">
+        <v>1795</v>
+      </c>
+      <c r="W10" s="71">
+        <v>0</v>
+      </c>
+      <c r="X10" s="71">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="71">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="71">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="71">
+        <v>1721</v>
+      </c>
+      <c r="AB10" s="71">
+        <v>150</v>
+      </c>
+      <c r="AC10" s="71">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="71">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="71">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="71">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="71">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="71">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="71">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="71">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="71">
+        <v>0</v>
+      </c>
       <c r="AL10" s="56"/>
       <c r="AM10" s="56"/>
       <c r="AN10" s="56"/>
@@ -66540,43 +66616,119 @@
       <c r="AU10" s="56"/>
     </row>
     <row r="11" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A11" s="56"/>
-      <c r="B11" s="56"/>
-      <c r="C11" s="56"/>
-      <c r="D11" s="56"/>
-      <c r="E11" s="56"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="56"/>
-      <c r="H11" s="56"/>
-      <c r="I11" s="56"/>
-      <c r="J11" s="56"/>
-      <c r="K11" s="56"/>
-      <c r="L11" s="56"/>
-      <c r="M11" s="56"/>
-      <c r="N11" s="56"/>
-      <c r="O11" s="56"/>
-      <c r="P11" s="56"/>
-      <c r="Q11" s="56"/>
-      <c r="R11" s="56"/>
-      <c r="S11" s="56"/>
-      <c r="T11" s="56"/>
-      <c r="U11" s="56"/>
-      <c r="V11" s="56"/>
-      <c r="W11" s="56"/>
-      <c r="X11" s="56"/>
-      <c r="Y11" s="56"/>
-      <c r="Z11" s="56"/>
-      <c r="AA11" s="56"/>
-      <c r="AB11" s="56"/>
-      <c r="AC11" s="56"/>
-      <c r="AD11" s="56"/>
-      <c r="AE11" s="56"/>
-      <c r="AF11" s="56"/>
-      <c r="AG11" s="56"/>
-      <c r="AH11" s="56"/>
-      <c r="AI11" s="56"/>
-      <c r="AJ11" s="56"/>
-      <c r="AK11" s="56"/>
+      <c r="A11" s="61" t="inlineStr">
+        <is>
+          <t>IRP25_GAS</t>
+        </is>
+      </c>
+      <c r="B11" s="68">
+        <v>1</v>
+      </c>
+      <c r="C11" s="69" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="70" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="70" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="71">
+        <v>0</v>
+      </c>
+      <c r="H11" s="71">
+        <v>0</v>
+      </c>
+      <c r="I11" s="71">
+        <v>0</v>
+      </c>
+      <c r="J11" s="71">
+        <v>0</v>
+      </c>
+      <c r="K11" s="71">
+        <v>0</v>
+      </c>
+      <c r="L11" s="71">
+        <v>0</v>
+      </c>
+      <c r="M11" s="71">
+        <v>0</v>
+      </c>
+      <c r="N11" s="71">
+        <v>0</v>
+      </c>
+      <c r="O11" s="71">
+        <v>0</v>
+      </c>
+      <c r="P11" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="71">
+        <v>4205</v>
+      </c>
+      <c r="R11" s="71">
+        <v>0</v>
+      </c>
+      <c r="S11" s="71">
+        <v>0</v>
+      </c>
+      <c r="T11" s="71">
+        <v>0</v>
+      </c>
+      <c r="U11" s="71">
+        <v>0</v>
+      </c>
+      <c r="V11" s="71">
+        <v>4205</v>
+      </c>
+      <c r="W11" s="71">
+        <v>0</v>
+      </c>
+      <c r="X11" s="71">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="71">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="71">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="71">
+        <v>4029</v>
+      </c>
+      <c r="AB11" s="71">
+        <v>350</v>
+      </c>
+      <c r="AC11" s="71">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="71">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="71">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="71">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="71">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="71">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="71">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="71">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="71">
+        <v>0</v>
+      </c>
       <c r="AL11" s="56"/>
       <c r="AM11" s="56"/>
       <c r="AN11" s="56"/>
